--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -2052,45 +2052,45 @@
   <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.46875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.9140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="24.91796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.2734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.2578125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.44140625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.16796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.265625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.16796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="80.89453125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.91796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="23.2734375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.2109375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.55078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.87109375" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="36" max="36" width="156.82421875" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="40.80859375" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="156.828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="40.8125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="107.39453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="40.0703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -1859,21 +1856,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2216,7 +2198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2328,7 +2310,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2442,7 +2424,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2554,7 +2536,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2668,7 +2650,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2782,7 +2764,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2896,7 +2878,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3010,7 +2992,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3124,7 +3106,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3240,7 +3222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3256,7 +3238,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>81</v>
@@ -3352,7 +3334,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>145</v>
       </c>
@@ -3468,7 +3450,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -3586,7 +3568,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>173</v>
       </c>
@@ -3602,7 +3584,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -3700,7 +3682,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>173</v>
       </c>
@@ -3818,7 +3800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>184</v>
       </c>
@@ -3930,7 +3912,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>188</v>
       </c>
@@ -4044,7 +4026,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -4160,7 +4142,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>204</v>
       </c>
@@ -4276,7 +4258,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>212</v>
       </c>
@@ -4390,7 +4372,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>220</v>
       </c>
@@ -4504,7 +4486,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>228</v>
       </c>
@@ -4616,7 +4598,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>234</v>
       </c>
@@ -4728,7 +4710,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -4842,7 +4824,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>248</v>
       </c>
@@ -4958,7 +4940,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>257</v>
       </c>
@@ -5074,7 +5056,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>267</v>
       </c>
@@ -5190,7 +5172,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>277</v>
       </c>
@@ -5306,7 +5288,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>285</v>
       </c>
@@ -5422,7 +5404,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>294</v>
       </c>
@@ -5534,7 +5516,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>295</v>
       </c>
@@ -5648,7 +5630,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>295</v>
       </c>
@@ -5663,7 +5645,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
@@ -5762,7 +5744,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>295</v>
       </c>
@@ -5777,7 +5759,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -5876,7 +5858,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>304</v>
       </c>
@@ -5992,7 +5974,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>314</v>
       </c>
@@ -6106,7 +6088,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>323</v>
       </c>
@@ -6222,7 +6204,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>330</v>
       </c>
@@ -6334,7 +6316,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>337</v>
       </c>
@@ -6446,7 +6428,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>345</v>
       </c>
@@ -6560,7 +6542,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>354</v>
       </c>
@@ -6672,7 +6654,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>361</v>
       </c>
@@ -6784,7 +6766,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>369</v>
       </c>
@@ -6898,7 +6880,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>376</v>
       </c>
@@ -7012,7 +6994,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>383</v>
       </c>
@@ -7124,7 +7106,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>393</v>
       </c>
@@ -7240,7 +7222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>401</v>
       </c>
@@ -7356,7 +7338,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>409</v>
       </c>
@@ -7472,7 +7454,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>417</v>
       </c>
@@ -7584,7 +7566,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>418</v>
       </c>
@@ -7698,7 +7680,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>419</v>
       </c>
@@ -7814,7 +7796,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>424</v>
       </c>
@@ -7928,7 +7910,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>432</v>
       </c>
@@ -8042,7 +8024,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>437</v>
       </c>
@@ -8158,7 +8140,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>442</v>
       </c>
@@ -8272,7 +8254,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>447</v>
       </c>
@@ -8386,7 +8368,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>451</v>
       </c>
@@ -8500,7 +8482,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>459</v>
       </c>
@@ -8612,7 +8594,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>463</v>
       </c>
@@ -8728,7 +8710,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>470</v>
       </c>
@@ -8840,7 +8822,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>471</v>
       </c>
@@ -8954,7 +8936,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>472</v>
       </c>
@@ -9070,7 +9052,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>473</v>
       </c>
@@ -9186,7 +9168,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>481</v>
       </c>
@@ -9302,7 +9284,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>489</v>
       </c>
@@ -9414,7 +9396,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>489</v>
       </c>
@@ -9530,7 +9512,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>499</v>
       </c>
@@ -9642,7 +9624,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>500</v>
       </c>
@@ -9756,7 +9738,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>501</v>
       </c>
@@ -9870,7 +9852,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>507</v>
       </c>
@@ -9984,7 +9966,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>514</v>
       </c>
@@ -10098,7 +10080,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>518</v>
       </c>
@@ -10212,7 +10194,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>523</v>
       </c>
@@ -10328,7 +10310,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>529</v>
       </c>
@@ -10444,7 +10426,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>535</v>
       </c>
@@ -10556,7 +10538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>536</v>
       </c>
@@ -10670,7 +10652,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>537</v>
       </c>
@@ -10786,7 +10768,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>538</v>
       </c>
@@ -10900,7 +10882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>544</v>
       </c>
@@ -11013,24 +10995,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN78">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$78</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -1856,6 +1859,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2198,7 +2216,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2310,7 +2328,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2424,7 +2442,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2536,7 +2554,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2650,7 +2668,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2764,7 +2782,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2878,7 +2896,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2992,7 +3010,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3106,7 +3124,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3222,7 +3240,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3238,7 +3256,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>81</v>
@@ -3334,7 +3352,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>145</v>
       </c>
@@ -3450,7 +3468,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
@@ -3568,7 +3586,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>173</v>
       </c>
@@ -3584,7 +3602,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -3682,7 +3700,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>173</v>
       </c>
@@ -3800,7 +3818,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>184</v>
       </c>
@@ -3912,7 +3930,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>188</v>
       </c>
@@ -4026,7 +4044,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -4142,7 +4160,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>204</v>
       </c>
@@ -4258,7 +4276,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>212</v>
       </c>
@@ -4372,7 +4390,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>220</v>
       </c>
@@ -4486,7 +4504,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>228</v>
       </c>
@@ -4598,7 +4616,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>234</v>
       </c>
@@ -4710,7 +4728,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -4824,7 +4842,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>248</v>
       </c>
@@ -4940,7 +4958,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>257</v>
       </c>
@@ -5056,7 +5074,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>267</v>
       </c>
@@ -5172,7 +5190,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>277</v>
       </c>
@@ -5288,7 +5306,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>285</v>
       </c>
@@ -5404,7 +5422,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>294</v>
       </c>
@@ -5516,7 +5534,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>295</v>
       </c>
@@ -5630,7 +5648,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>295</v>
       </c>
@@ -5645,7 +5663,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
@@ -5744,7 +5762,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>295</v>
       </c>
@@ -5759,7 +5777,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -5858,7 +5876,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>304</v>
       </c>
@@ -5974,7 +5992,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>314</v>
       </c>
@@ -6088,7 +6106,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>323</v>
       </c>
@@ -6204,7 +6222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>330</v>
       </c>
@@ -6316,7 +6334,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>337</v>
       </c>
@@ -6428,7 +6446,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>345</v>
       </c>
@@ -6542,7 +6560,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>354</v>
       </c>
@@ -6654,7 +6672,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>361</v>
       </c>
@@ -6766,7 +6784,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>369</v>
       </c>
@@ -6880,7 +6898,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>376</v>
       </c>
@@ -6994,7 +7012,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>383</v>
       </c>
@@ -7106,7 +7124,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>393</v>
       </c>
@@ -7222,7 +7240,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>401</v>
       </c>
@@ -7338,7 +7356,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>409</v>
       </c>
@@ -7454,7 +7472,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>417</v>
       </c>
@@ -7566,7 +7584,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>418</v>
       </c>
@@ -7680,7 +7698,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>419</v>
       </c>
@@ -7796,7 +7814,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>424</v>
       </c>
@@ -7910,7 +7928,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>432</v>
       </c>
@@ -8024,7 +8042,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>437</v>
       </c>
@@ -8140,7 +8158,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>442</v>
       </c>
@@ -8254,7 +8272,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>447</v>
       </c>
@@ -8368,7 +8386,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>451</v>
       </c>
@@ -8482,7 +8500,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>459</v>
       </c>
@@ -8594,7 +8612,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>463</v>
       </c>
@@ -8710,7 +8728,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>470</v>
       </c>
@@ -8822,7 +8840,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>471</v>
       </c>
@@ -8936,7 +8954,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>472</v>
       </c>
@@ -9052,7 +9070,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>473</v>
       </c>
@@ -9168,7 +9186,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>481</v>
       </c>
@@ -9284,7 +9302,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>489</v>
       </c>
@@ -9396,7 +9414,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>489</v>
       </c>
@@ -9512,7 +9530,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>499</v>
       </c>
@@ -9624,7 +9642,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>500</v>
       </c>
@@ -9738,7 +9756,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>501</v>
       </c>
@@ -9852,7 +9870,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>507</v>
       </c>
@@ -9966,7 +9984,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>514</v>
       </c>
@@ -10080,7 +10098,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>518</v>
       </c>
@@ -10194,7 +10212,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>523</v>
       </c>
@@ -10310,7 +10328,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>529</v>
       </c>
@@ -10426,7 +10444,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>535</v>
       </c>
@@ -10538,7 +10556,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>536</v>
       </c>
@@ -10652,7 +10670,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>537</v>
       </c>
@@ -10768,7 +10786,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>538</v>
       </c>
@@ -10882,7 +10900,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>544</v>
       </c>
@@ -10995,6 +11013,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN78">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI77">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -287,7 +287,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">id
 </t>
   </si>
   <si>
@@ -593,6 +593,10 @@
   </si>
   <si>
     <t>Patient.name.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -3825,13 +3829,13 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -3882,7 +3886,7 @@
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>79</v>
@@ -3914,7 +3918,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3943,7 +3947,7 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>137</v>
@@ -3984,10 +3988,10 @@
         <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>81</v>
@@ -3996,7 +4000,7 @@
         <v>151</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
@@ -4028,7 +4032,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4054,16 +4058,16 @@
         <v>108</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>81</v>
@@ -4088,13 +4092,13 @@
         <v>81</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>81</v>
@@ -4112,7 +4116,7 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>79</v>
@@ -4127,7 +4131,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4136,7 +4140,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -4144,7 +4148,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4167,19 +4171,19 @@
         <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>81</v>
@@ -4228,7 +4232,7 @@
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>79</v>
@@ -4243,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4252,7 +4256,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4260,11 +4264,11 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4283,16 +4287,16 @@
         <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -4342,7 +4346,7 @@
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>79</v>
@@ -4357,7 +4361,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4366,7 +4370,7 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4374,11 +4378,11 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4397,16 +4401,16 @@
         <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4456,7 +4460,7 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
@@ -4471,7 +4475,7 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4480,7 +4484,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4488,7 +4492,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4511,13 +4515,13 @@
         <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -4568,7 +4572,7 @@
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4583,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4592,7 +4596,7 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4600,7 +4604,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4623,13 +4627,13 @@
         <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4680,7 +4684,7 @@
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
@@ -4695,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4704,7 +4708,7 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4712,7 +4716,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4735,17 +4739,17 @@
         <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>81</v>
@@ -4794,7 +4798,7 @@
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>79</v>
@@ -4809,7 +4813,7 @@
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4818,7 +4822,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4826,7 +4830,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4849,19 +4853,19 @@
         <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>81</v>
@@ -4910,7 +4914,7 @@
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
@@ -4925,16 +4929,16 @@
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4942,7 +4946,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4968,16 +4972,16 @@
         <v>108</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>81</v>
@@ -5002,13 +5006,13 @@
         <v>81</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>81</v>
@@ -5026,7 +5030,7 @@
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>79</v>
@@ -5041,16 +5045,16 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5058,7 +5062,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5081,19 +5085,19 @@
         <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O27" t="s" s="2">
         <v>81</v>
@@ -5142,7 +5146,7 @@
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
@@ -5157,24 +5161,24 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5197,19 +5201,19 @@
         <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>81</v>
@@ -5258,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
@@ -5273,7 +5277,7 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>171</v>
@@ -5282,7 +5286,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5290,7 +5294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5313,19 +5317,19 @@
         <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>81</v>
@@ -5374,7 +5378,7 @@
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
@@ -5389,16 +5393,16 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5406,7 +5410,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5429,13 +5433,13 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5486,7 +5490,7 @@
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
@@ -5518,7 +5522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5547,7 +5551,7 @@
         <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>137</v>
@@ -5588,10 +5592,10 @@
         <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>81</v>
@@ -5600,7 +5604,7 @@
         <v>151</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5632,10 +5636,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>81</v>
@@ -5657,13 +5661,13 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5714,7 +5718,7 @@
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>79</v>
@@ -5746,10 +5750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>81</v>
@@ -5771,13 +5775,13 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5828,7 +5832,7 @@
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -5860,7 +5864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5886,16 +5890,16 @@
         <v>108</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>81</v>
@@ -5908,7 +5912,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5920,13 +5924,13 @@
         <v>81</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>81</v>
@@ -5944,7 +5948,7 @@
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>79</v>
@@ -5959,7 +5963,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -5968,7 +5972,7 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5976,7 +5980,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6002,13 +6006,13 @@
         <v>108</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6022,7 +6026,7 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>81</v>
@@ -6034,13 +6038,13 @@
         <v>81</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>81</v>
@@ -6058,7 +6062,7 @@
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>79</v>
@@ -6073,7 +6077,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6082,7 +6086,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6090,7 +6094,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6113,19 +6117,19 @@
         <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>81</v>
@@ -6138,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6174,7 +6178,7 @@
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>79</v>
@@ -6189,7 +6193,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6198,7 +6202,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6206,7 +6210,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6229,13 +6233,13 @@
         <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -6250,7 +6254,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6286,7 +6290,7 @@
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6301,7 +6305,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6310,7 +6314,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6318,11 +6322,11 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6341,13 +6345,13 @@
         <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6362,7 +6366,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6398,7 +6402,7 @@
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>79</v>
@@ -6413,7 +6417,7 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6422,7 +6426,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6430,11 +6434,11 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6453,16 +6457,16 @@
         <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6476,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6512,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>79</v>
@@ -6527,7 +6531,7 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6536,7 +6540,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6544,11 +6548,11 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6567,13 +6571,13 @@
         <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6624,7 +6628,7 @@
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>79</v>
@@ -6639,7 +6643,7 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6648,7 +6652,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6656,11 +6660,11 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6679,13 +6683,13 @@
         <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6700,7 +6704,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -6736,7 +6740,7 @@
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>79</v>
@@ -6751,7 +6755,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -6760,7 +6764,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6768,7 +6772,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6791,16 +6795,16 @@
         <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6850,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>79</v>
@@ -6865,7 +6869,7 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -6874,7 +6878,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6882,7 +6886,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6905,17 +6909,17 @@
         <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>81</v>
@@ -6928,7 +6932,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>81</v>
@@ -6964,7 +6968,7 @@
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>79</v>
@@ -6979,7 +6983,7 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6988,7 +6992,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6996,7 +7000,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7019,17 +7023,17 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>81</v>
@@ -7054,11 +7058,11 @@
         <v>81</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>81</v>
@@ -7076,7 +7080,7 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>79</v>
@@ -7091,16 +7095,16 @@
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7108,7 +7112,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7131,19 +7135,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>81</v>
@@ -7192,7 +7196,7 @@
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
@@ -7207,7 +7211,7 @@
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>171</v>
@@ -7216,7 +7220,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7224,7 +7228,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7247,19 +7251,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>81</v>
@@ -7308,7 +7312,7 @@
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
@@ -7323,7 +7327,7 @@
         <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>171</v>
@@ -7332,7 +7336,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7340,7 +7344,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7363,19 +7367,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>81</v>
@@ -7424,7 +7428,7 @@
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7436,10 +7440,10 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>171</v>
@@ -7456,7 +7460,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7479,13 +7483,13 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7536,7 +7540,7 @@
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>79</v>
@@ -7568,7 +7572,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7597,7 +7601,7 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>137</v>
@@ -7650,7 +7654,7 @@
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7682,11 +7686,11 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7708,10 +7712,10 @@
         <v>134</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>137</v>
@@ -7766,7 +7770,7 @@
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
@@ -7798,7 +7802,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7821,17 +7825,17 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>81</v>
@@ -7856,13 +7860,13 @@
         <v>81</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>81</v>
@@ -7880,7 +7884,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
@@ -7895,7 +7899,7 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>171</v>
@@ -7904,7 +7908,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7912,7 +7916,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7938,14 +7942,14 @@
         <v>174</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>81</v>
@@ -7994,7 +7998,7 @@
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
@@ -8018,7 +8022,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8026,7 +8030,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8049,19 +8053,19 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>81</v>
@@ -8110,7 +8114,7 @@
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -8125,7 +8129,7 @@
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>171</v>
@@ -8134,7 +8138,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8142,7 +8146,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8165,17 +8169,17 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>81</v>
@@ -8224,7 +8228,7 @@
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
@@ -8239,7 +8243,7 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>171</v>
@@ -8248,7 +8252,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8256,7 +8260,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8282,14 +8286,14 @@
         <v>108</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>81</v>
@@ -8314,13 +8318,13 @@
         <v>81</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>81</v>
@@ -8338,7 +8342,7 @@
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>79</v>
@@ -8353,7 +8357,7 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>171</v>
@@ -8362,7 +8366,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8370,7 +8374,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8393,17 +8397,17 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>81</v>
@@ -8452,7 +8456,7 @@
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>79</v>
@@ -8461,13 +8465,13 @@
         <v>88</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>171</v>
@@ -8476,7 +8480,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8484,7 +8488,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8507,13 +8511,13 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8564,7 +8568,7 @@
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
@@ -8579,7 +8583,7 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>171</v>
@@ -8596,7 +8600,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8619,19 +8623,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>81</v>
@@ -8680,7 +8684,7 @@
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
@@ -8695,10 +8699,10 @@
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -8712,7 +8716,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8735,13 +8739,13 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8792,7 +8796,7 @@
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
@@ -8824,7 +8828,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8853,7 +8857,7 @@
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>137</v>
@@ -8906,7 +8910,7 @@
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
@@ -8938,11 +8942,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8964,10 +8968,10 @@
         <v>134</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>137</v>
@@ -9022,7 +9026,7 @@
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
@@ -9054,7 +9058,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9077,19 +9081,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>81</v>
@@ -9138,7 +9142,7 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>88</v>
@@ -9153,16 +9157,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9170,7 +9174,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9196,16 +9200,16 @@
         <v>164</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>81</v>
@@ -9254,7 +9258,7 @@
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
@@ -9269,16 +9273,16 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9286,11 +9290,11 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9309,16 +9313,16 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9356,7 +9360,7 @@
         <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AB64" s="2"/>
       <c r="AC64" t="s" s="2">
@@ -9366,7 +9370,7 @@
         <v>151</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
@@ -9381,7 +9385,7 @@
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>171</v>
@@ -9390,7 +9394,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9398,13 +9402,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9423,16 +9427,16 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9482,7 +9486,7 @@
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>79</v>
@@ -9497,7 +9501,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>171</v>
@@ -9506,7 +9510,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9514,7 +9518,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9537,13 +9541,13 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9594,7 +9598,7 @@
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
@@ -9626,7 +9630,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9655,7 +9659,7 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>137</v>
@@ -9696,10 +9700,10 @@
         <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC67" t="s" s="2">
         <v>81</v>
@@ -9708,7 +9712,7 @@
         <v>151</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9740,7 +9744,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9763,16 +9767,16 @@
         <v>89</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
@@ -9822,7 +9826,7 @@
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
@@ -9831,7 +9835,7 @@
         <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
@@ -9854,7 +9858,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9880,13 +9884,13 @@
         <v>102</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
@@ -9912,13 +9916,13 @@
         <v>81</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>81</v>
@@ -9936,7 +9940,7 @@
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
@@ -9968,7 +9972,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9991,7 +9995,7 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>158</v>
@@ -10000,7 +10004,7 @@
         <v>159</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10050,7 +10054,7 @@
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
@@ -10082,7 +10086,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10105,16 +10109,16 @@
         <v>89</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10164,7 +10168,7 @@
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
@@ -10196,7 +10200,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10219,19 +10223,19 @@
         <v>89</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>81</v>
@@ -10280,7 +10284,7 @@
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10295,10 +10299,10 @@
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
@@ -10312,7 +10316,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10335,19 +10339,19 @@
         <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>81</v>
@@ -10396,7 +10400,7 @@
         <v>81</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>79</v>
@@ -10411,7 +10415,7 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>171</v>
@@ -10428,7 +10432,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10451,13 +10455,13 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10508,7 +10512,7 @@
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
@@ -10540,7 +10544,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10569,7 +10573,7 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>137</v>
@@ -10622,7 +10626,7 @@
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
@@ -10654,11 +10658,11 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10680,10 +10684,10 @@
         <v>134</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>137</v>
@@ -10738,7 +10742,7 @@
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10770,7 +10774,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10793,16 +10797,16 @@
         <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
@@ -10852,7 +10856,7 @@
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>88</v>
@@ -10876,7 +10880,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -10884,7 +10888,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10910,10 +10914,10 @@
         <v>108</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10940,13 +10944,13 @@
         <v>81</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>81</v>
@@ -10964,7 +10968,7 @@
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>88</v>
@@ -10979,7 +10983,7 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>171</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$94</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="601">
   <si>
     <t>Property</t>
   </si>
@@ -114,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -498,6 +501,203 @@
   </si>
   <si>
     <t>PID-3</t>
+  </si>
+  <si>
+    <t>Patient.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Patient.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Patient.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique within the system.</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Patient.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>cpr</t>
@@ -551,9 +751,6 @@
     <t>statusCode</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
@@ -580,6 +777,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-8:Patient.name.given or Patient.name.family or both SHALL be present {family.exists() or given.exists()}</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -595,35 +796,9 @@
     <t>Patient.name.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.name.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Patient.name.use</t>
   </si>
   <si>
@@ -637,9 +812,6 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -768,10 +940,6 @@
   </si>
   <si>
     <t>Patient.name.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Time period when name was/is in use</t>
@@ -1213,10 +1381,6 @@
     <t>Patient.maritalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Marital (civil) status of a patient</t>
   </si>
   <si>
@@ -1224,9 +1388,6 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.dk/fhir/core/ValueSet/dk-marital-status</t>
@@ -1425,10 +1586,6 @@
   </si>
   <si>
     <t>Patient.contact.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
   </si>
   <si>
     <t>Organization that is associated with the contact</t>
@@ -1860,6 +2017,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2035,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN78"/>
+  <dimension ref="A1:AN94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
@@ -2061,7 +2233,7 @@
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="80.89453125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="23.2734375" customWidth="true" bestFit="true"/>
@@ -2202,7 +2374,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2314,7 +2486,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2428,7 +2600,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2540,7 +2712,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2654,7 +2826,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2768,7 +2940,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2882,7 +3054,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2996,7 +3168,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3110,7 +3282,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3226,7 +3398,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3242,7 +3414,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>81</v>
@@ -3338,13 +3510,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B12" t="s" s="2">
         <v>156</v>
       </c>
+      <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3374,9 +3544,7 @@
         <v>159</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3424,19 +3592,19 @@
         <v>81</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>161</v>
@@ -3448,133 +3616,129 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="AB13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AE13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="AF13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3585,31 +3749,31 @@
         <v>79</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>81</v>
@@ -3634,35 +3798,37 @@
         <v>81</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AB14" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AC14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>81</v>
@@ -3671,28 +3837,26 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3713,19 +3877,19 @@
         <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>81</v>
@@ -3750,13 +3914,13 @@
         <v>81</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>81</v>
@@ -3774,13 +3938,13 @@
         <v>81</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>81</v>
@@ -3789,16 +3953,16 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3806,7 +3970,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3814,31 +3978,35 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="O16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3850,7 +4018,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3886,7 +4054,7 @@
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>79</v>
@@ -3898,10 +4066,10 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -3910,7 +4078,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3918,39 +4086,39 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -3964,7 +4132,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -3988,34 +4156,34 @@
         <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -4024,15 +4192,15 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>81</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4040,7 +4208,7 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>88</v>
@@ -4049,32 +4217,28 @@
         <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>81</v>
@@ -4092,13 +4256,13 @@
         <v>81</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>81</v>
@@ -4116,7 +4280,7 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>79</v>
@@ -4131,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4140,15 +4304,15 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4171,20 +4335,18 @@
         <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4232,7 +4394,7 @@
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>79</v>
@@ -4247,7 +4409,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4256,7 +4418,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4264,41 +4426,43 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="C20" t="s" s="2">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4346,22 +4510,22 @@
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>218</v>
+        <v>145</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4370,26 +4534,26 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>81</v>
@@ -4398,20 +4562,18 @@
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>81</v>
@@ -4460,22 +4622,22 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4484,19 +4646,19 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4512,18 +4674,20 @@
         <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>81</v>
@@ -4560,19 +4724,19 @@
         <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4584,10 +4748,10 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4596,15 +4760,15 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4615,28 +4779,32 @@
         <v>79</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>168</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4660,13 +4828,13 @@
         <v>81</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>81</v>
@@ -4684,13 +4852,13 @@
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>81</v>
@@ -4699,7 +4867,7 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4708,15 +4876,15 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>131</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4739,17 +4907,19 @@
         <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="N24" t="s" s="2">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>81</v>
@@ -4774,13 +4944,13 @@
         <v>81</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>81</v>
@@ -4798,7 +4968,7 @@
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>79</v>
@@ -4813,7 +4983,7 @@
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4822,7 +4992,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4830,7 +5000,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4838,13 +5008,13 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4853,19 +5023,19 @@
         <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>190</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>81</v>
@@ -4878,7 +5048,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -4914,13 +5084,13 @@
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>81</v>
@@ -4929,16 +5099,16 @@
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>255</v>
+        <v>195</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4946,7 +5116,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4954,13 +5124,13 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -4969,20 +5139,18 @@
         <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>81</v>
       </c>
@@ -4994,7 +5162,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -5006,13 +5174,13 @@
         <v>81</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>81</v>
@@ -5030,7 +5198,7 @@
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>79</v>
@@ -5045,24 +5213,24 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>265</v>
+        <v>203</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5085,20 +5253,16 @@
         <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5146,7 +5310,7 @@
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
@@ -5161,24 +5325,24 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>274</v>
+        <v>210</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5195,26 +5359,24 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>279</v>
+        <v>213</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5262,7 +5424,7 @@
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>278</v>
+        <v>217</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
@@ -5277,16 +5439,16 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5294,7 +5456,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5302,39 +5464,41 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>231</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="P29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="Q29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5378,13 +5542,13 @@
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>81</v>
@@ -5393,24 +5557,24 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>161</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5418,31 +5582,35 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5478,43 +5646,41 @@
         <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="AB30" s="2"/>
       <c r="AC30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5522,41 +5688,45 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B31" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="C31" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5592,19 +5762,19 @@
         <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5616,31 +5786,29 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5661,13 +5829,13 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>298</v>
+        <v>157</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>159</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5718,22 +5886,22 @@
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5748,22 +5916,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -5775,15 +5941,17 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>302</v>
+        <v>134</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M33" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>81</v>
@@ -5820,19 +5988,19 @@
         <v>81</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -5847,7 +6015,7 @@
         <v>139</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
@@ -5862,9 +6030,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5872,7 +6040,7 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>88</v>
@@ -5890,29 +6058,29 @@
         <v>108</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>252</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>253</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="R34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5924,13 +6092,13 @@
         <v>81</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>81</v>
@@ -5948,7 +6116,7 @@
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>79</v>
@@ -5963,7 +6131,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -5972,15 +6140,15 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6003,18 +6171,20 @@
         <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6026,7 +6196,7 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>319</v>
+        <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>81</v>
@@ -6038,13 +6208,13 @@
         <v>81</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>321</v>
+        <v>81</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6232,7 @@
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>322</v>
+        <v>265</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>79</v>
@@ -6077,7 +6247,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6086,23 +6256,23 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>88</v>
@@ -6117,20 +6287,18 @@
         <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>270</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>271</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6142,7 +6310,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6178,7 +6346,7 @@
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>79</v>
@@ -6193,7 +6361,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>211</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6202,19 +6370,19 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>275</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6233,15 +6401,17 @@
         <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>81</v>
@@ -6254,7 +6424,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6290,7 +6460,7 @@
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>335</v>
+        <v>281</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6305,7 +6475,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6314,26 +6484,26 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>283</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
@@ -6345,13 +6515,13 @@
         <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6366,7 +6536,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6402,13 +6572,13 @@
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -6417,7 +6587,7 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6426,26 +6596,26 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>81</v>
@@ -6457,17 +6627,15 @@
         <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>348</v>
+        <v>291</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
         <v>81</v>
@@ -6480,7 +6648,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6516,13 +6684,13 @@
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -6531,7 +6699,7 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6540,19 +6708,19 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>356</v>
+        <v>81</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6571,16 +6739,18 @@
         <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
+      <c r="N40" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6628,7 +6798,7 @@
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>79</v>
@@ -6643,7 +6813,7 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>360</v>
+        <v>301</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6652,26 +6822,26 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>361</v>
+        <v>302</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>303</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -6683,16 +6853,20 @@
         <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>185</v>
+        <v>304</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>305</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6704,7 +6878,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -6740,13 +6914,13 @@
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>81</v>
@@ -6755,16 +6929,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>368</v>
+        <v>309</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>311</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6772,7 +6946,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6780,13 +6954,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6795,18 +6969,20 @@
         <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>313</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6830,13 +7006,13 @@
         <v>81</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>81</v>
@@ -6854,7 +7030,7 @@
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>79</v>
@@ -6869,16 +7045,16 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>321</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6886,7 +7062,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>322</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6900,7 +7076,7 @@
         <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -6909,17 +7085,19 @@
         <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>242</v>
+        <v>323</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M43" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="N43" t="s" s="2">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>81</v>
@@ -6932,7 +7110,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>81</v>
@@ -6968,7 +7146,7 @@
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>79</v>
@@ -6983,24 +7161,24 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>330</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>331</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7017,23 +7195,25 @@
         <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="N44" t="s" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>81</v>
@@ -7058,11 +7238,13 @@
         <v>81</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="X44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Y44" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>81</v>
@@ -7080,7 +7262,7 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>79</v>
@@ -7095,24 +7277,24 @@
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>392</v>
+        <v>161</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7123,7 +7305,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7132,22 +7314,22 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>81</v>
@@ -7196,13 +7378,13 @@
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>81</v>
@@ -7211,24 +7393,24 @@
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>400</v>
+        <v>346</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>171</v>
+        <v>347</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>349</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7239,7 +7421,7 @@
         <v>79</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>81</v>
@@ -7251,20 +7433,16 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>403</v>
+        <v>157</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>404</v>
+        <v>158</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7312,43 +7490,43 @@
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>402</v>
+        <v>160</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>408</v>
+        <v>161</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>350</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7367,20 +7545,18 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>411</v>
+        <v>134</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>163</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7416,19 +7592,19 @@
         <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>410</v>
+        <v>166</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7440,13 +7616,13 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>416</v>
+        <v>139</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>417</v>
+        <v>161</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -7458,11 +7634,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B48" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="C48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7483,13 +7661,13 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>185</v>
+        <v>352</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>187</v>
+        <v>354</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7540,22 +7718,22 @@
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7570,20 +7748,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="B49" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="C49" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>81</v>
@@ -7595,17 +7775,15 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>134</v>
+        <v>356</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>357</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>81</v>
@@ -7654,7 +7832,7 @@
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7669,7 +7847,7 @@
         <v>139</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7684,20 +7862,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>359</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>81</v>
@@ -7709,19 +7887,19 @@
         <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>422</v>
+        <v>360</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>361</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>137</v>
+        <v>362</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>143</v>
+        <v>363</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>81</v>
@@ -7734,7 +7912,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -7746,13 +7924,13 @@
         <v>81</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>81</v>
@@ -7770,22 +7948,22 @@
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>424</v>
+        <v>367</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>131</v>
+        <v>258</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -7794,15 +7972,15 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7813,7 +7991,7 @@
         <v>79</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>81</v>
@@ -7822,21 +8000,21 @@
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>385</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="M51" s="2"/>
-      <c r="N51" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7848,7 +8026,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -7860,13 +8038,13 @@
         <v>81</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>389</v>
+        <v>172</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>429</v>
+        <v>374</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>430</v>
+        <v>375</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>81</v>
@@ -7884,13 +8062,13 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>425</v>
+        <v>376</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>81</v>
@@ -7899,24 +8077,24 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>431</v>
+        <v>258</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7936,20 +8114,22 @@
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M52" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="N52" t="s" s="2">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>81</v>
@@ -7962,7 +8142,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>81</v>
@@ -7998,7 +8178,7 @@
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>433</v>
+        <v>383</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
@@ -8013,24 +8193,24 @@
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>385</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8050,23 +8230,19 @@
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8078,7 +8254,7 @@
         <v>81</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>81</v>
@@ -8114,7 +8290,7 @@
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -8129,28 +8305,28 @@
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>255</v>
+        <v>390</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>81</v>
+        <v>393</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8166,21 +8342,19 @@
         <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>287</v>
+        <v>157</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>444</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="M54" s="2"/>
-      <c r="N54" t="s" s="2">
-        <v>446</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8192,7 +8366,7 @@
         <v>81</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>81</v>
@@ -8228,7 +8402,7 @@
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
@@ -8243,28 +8417,28 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>292</v>
+        <v>398</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>399</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>400</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8280,21 +8454,21 @@
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M55" s="2"/>
-      <c r="N55" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8306,7 +8480,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -8318,13 +8492,13 @@
         <v>81</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>199</v>
+        <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>264</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>81</v>
@@ -8342,7 +8516,7 @@
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>79</v>
@@ -8357,28 +8531,28 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>265</v>
+        <v>407</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8394,21 +8568,19 @@
         <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>453</v>
+        <v>157</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>454</v>
+        <v>411</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>412</v>
       </c>
       <c r="M56" s="2"/>
-      <c r="N56" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8456,7 +8628,7 @@
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>79</v>
@@ -8465,34 +8637,34 @@
         <v>88</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>457</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>459</v>
+        <v>415</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8508,16 +8680,16 @@
         <v>81</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>242</v>
+        <v>157</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>461</v>
+        <v>418</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>419</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8532,7 +8704,7 @@
         <v>81</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>81</v>
@@ -8568,7 +8740,7 @@
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
@@ -8583,24 +8755,24 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8611,7 +8783,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>81</v>
@@ -8620,23 +8792,21 @@
         <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>411</v>
+        <v>157</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>426</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8684,13 +8854,13 @@
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>81</v>
@@ -8699,24 +8869,24 @@
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>470</v>
+        <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>431</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8736,19 +8906,21 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>186</v>
+        <v>432</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>433</v>
       </c>
       <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
+      <c r="N59" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8760,7 +8932,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -8796,7 +8968,7 @@
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>188</v>
+        <v>436</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
@@ -8808,10 +8980,10 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -8820,26 +8992,26 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>81</v>
@@ -8851,18 +9023,18 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>439</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8886,13 +9058,11 @@
         <v>81</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>81</v>
@@ -8910,74 +9080,74 @@
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>193</v>
+        <v>438</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>171</v>
+        <v>443</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>134</v>
+        <v>447</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>137</v>
+        <v>450</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>143</v>
+        <v>451</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>81</v>
@@ -9026,39 +9196,39 @@
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>131</v>
+        <v>452</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9066,10 +9236,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>81</v>
@@ -9081,19 +9251,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>385</v>
+        <v>455</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>81</v>
@@ -9118,13 +9288,13 @@
         <v>81</v>
       </c>
       <c r="W62" t="s" s="2">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>81</v>
@@ -9142,13 +9312,13 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>81</v>
@@ -9157,24 +9327,24 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>480</v>
+        <v>161</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9185,7 +9355,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -9197,19 +9367,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>164</v>
+        <v>463</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>81</v>
@@ -9258,50 +9428,50 @@
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>100</v>
+        <v>468</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>488</v>
+        <v>161</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>81</v>
@@ -9313,17 +9483,15 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>492</v>
+        <v>157</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>493</v>
+        <v>158</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>81</v>
@@ -9360,55 +9528,55 @@
         <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AB64" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AC64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>490</v>
+        <v>160</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>497</v>
+        <v>161</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>498</v>
+        <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
-        <v>491</v>
+        <v>133</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9427,16 +9595,16 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>492</v>
+        <v>134</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>163</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>137</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9486,7 +9654,7 @@
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>490</v>
+        <v>166</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>79</v>
@@ -9498,59 +9666,63 @@
         <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>497</v>
+        <v>161</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>498</v>
+        <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>186</v>
+        <v>474</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9598,22 +9770,22 @@
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>188</v>
+        <v>476</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9628,13 +9800,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9653,18 +9825,18 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>478</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="M67" s="2"/>
+      <c r="N67" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9688,31 +9860,31 @@
         <v>81</v>
       </c>
       <c r="W67" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>81</v>
+        <v>482</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>191</v>
+        <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>192</v>
+        <v>81</v>
       </c>
       <c r="AC67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>193</v>
+        <v>477</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9724,27 +9896,27 @@
         <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>171</v>
+        <v>483</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9764,21 +9936,21 @@
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="M68" s="2"/>
+      <c r="N68" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O68" t="s" s="2">
         <v>81</v>
       </c>
@@ -9826,7 +9998,7 @@
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
@@ -9835,30 +10007,30 @@
         <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>507</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9869,7 +10041,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>81</v>
@@ -9878,21 +10050,23 @@
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>493</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O69" t="s" s="2">
         <v>81</v>
       </c>
@@ -9916,13 +10090,13 @@
         <v>81</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>81</v>
@@ -9940,13 +10114,13 @@
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>81</v>
@@ -9955,24 +10129,24 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9995,18 +10169,18 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>516</v>
+        <v>341</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>158</v>
+        <v>496</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="M70" s="2"/>
+      <c r="N70" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10054,7 +10228,7 @@
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
@@ -10063,30 +10237,30 @@
         <v>88</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>162</v>
+        <v>499</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10106,21 +10280,21 @@
         <v>81</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>520</v>
+        <v>313</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="M71" s="2"/>
+      <c r="N71" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10144,13 +10318,13 @@
         <v>81</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>318</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>81</v>
@@ -10168,7 +10342,7 @@
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
@@ -10183,24 +10357,24 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>131</v>
+        <v>319</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10220,22 +10394,20 @@
         <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>453</v>
+        <v>213</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="M72" s="2"/>
       <c r="N72" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>81</v>
@@ -10284,7 +10456,7 @@
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10293,30 +10465,30 @@
         <v>88</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>529</v>
+        <v>161</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10327,32 +10499,28 @@
         <v>79</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>411</v>
+        <v>206</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10400,13 +10568,13 @@
         <v>81</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>81</v>
@@ -10415,10 +10583,10 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
@@ -10430,9 +10598,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10443,7 +10611,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>81</v>
@@ -10455,16 +10623,20 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>185</v>
+        <v>463</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>186</v>
+        <v>516</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="O74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10512,25 +10684,25 @@
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>188</v>
+        <v>515</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>171</v>
+        <v>520</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
@@ -10542,20 +10714,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>81</v>
@@ -10567,17 +10739,15 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
         <v>81</v>
@@ -10626,22 +10796,22 @@
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -10656,13 +10826,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>421</v>
+        <v>133</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10675,26 +10845,24 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>134</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>422</v>
+        <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>423</v>
+        <v>163</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="N76" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
         <v>81</v>
       </c>
@@ -10742,7 +10910,7 @@
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>424</v>
+        <v>166</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10757,7 +10925,7 @@
         <v>139</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -10772,43 +10940,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>540</v>
+        <v>134</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>542</v>
+        <v>475</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>81</v>
       </c>
@@ -10856,39 +11026,39 @@
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>539</v>
+        <v>476</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>544</v>
+        <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10908,19 +11078,23 @@
         <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="O78" t="s" s="2">
         <v>81</v>
       </c>
@@ -10944,13 +11118,13 @@
         <v>81</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>547</v>
+        <v>113</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>548</v>
+        <v>114</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>81</v>
@@ -10968,7 +11142,7 @@
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>88</v>
@@ -10983,22 +11157,1866 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P80" s="2"/>
+      <c r="Q80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AB80" s="2"/>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P84" s="2"/>
+      <c r="Q84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P85" s="2"/>
+      <c r="Q85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P86" s="2"/>
+      <c r="Q86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P92" s="2"/>
+      <c r="Q92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P93" s="2"/>
+      <c r="Q93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P94" s="2"/>
+      <c r="Q94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN94">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI93">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$94</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="550">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -117,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-patient</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -501,203 +498,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>Patient.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Patient.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Patient.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique within the system.</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Patient.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Patient.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>cpr</t>
@@ -751,6 +551,9 @@
     <t>statusCode</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>FiveWs.status</t>
   </si>
   <si>
@@ -777,10 +580,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-8:Patient.name.given or Patient.name.family or both SHALL be present {family.exists() or given.exists()}</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -796,9 +595,35 @@
     <t>Patient.name.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>Patient.name.extension</t>
   </si>
   <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
     <t>Patient.name.use</t>
   </si>
   <si>
@@ -812,6 +637,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -940,6 +768,10 @@
   </si>
   <si>
     <t>Patient.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
   </si>
   <si>
     <t>Time period when name was/is in use</t>
@@ -1381,6 +1213,10 @@
     <t>Patient.maritalStatus</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
     <t>Marital (civil) status of a patient</t>
   </si>
   <si>
@@ -1388,6 +1224,9 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.dk/fhir/core/ValueSet/dk-marital-status</t>
@@ -1586,6 +1425,10 @@
   </si>
   <si>
     <t>Patient.contact.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
   </si>
   <si>
     <t>Organization that is associated with the contact</t>
@@ -2017,21 +1860,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2207,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN94"/>
+  <dimension ref="A1:AN78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
@@ -2233,7 +2061,7 @@
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="80.89453125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="23.2734375" customWidth="true" bestFit="true"/>
@@ -2374,7 +2202,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2486,7 +2314,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2600,7 +2428,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2712,7 +2540,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2826,7 +2654,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2940,7 +2768,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -3054,7 +2882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3168,7 +2996,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3282,7 +3110,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3398,7 +3226,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3414,7 +3242,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>81</v>
@@ -3510,11 +3338,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3544,7 +3374,9 @@
         <v>159</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="N12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3592,19 +3424,19 @@
         <v>81</v>
       </c>
       <c r="AE12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AF12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AI12" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>161</v>
@@ -3616,118 +3448,122 @@
         <v>81</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Q13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M13" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P13" s="2"/>
-      <c r="Q13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="AF13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>81</v>
@@ -3736,9 +3572,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3749,31 +3585,31 @@
         <v>79</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>81</v>
@@ -3798,37 +3634,35 @@
         <v>81</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AB14" s="2"/>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="AF14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>81</v>
@@ -3837,26 +3671,28 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="C15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3877,19 +3713,19 @@
         <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>81</v>
@@ -3914,13 +3750,13 @@
         <v>81</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Z15" t="s" s="2">
         <v>81</v>
@@ -3938,13 +3774,13 @@
         <v>81</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>81</v>
@@ -3953,16 +3789,16 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3970,7 +3806,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3978,35 +3814,31 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
         <v>81</v>
       </c>
@@ -4018,7 +3850,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -4054,7 +3886,7 @@
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>79</v>
@@ -4066,10 +3898,10 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -4078,7 +3910,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -4086,39 +3918,39 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -4132,7 +3964,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -4156,34 +3988,34 @@
         <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -4192,15 +4024,15 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4208,7 +4040,7 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>88</v>
@@ -4217,28 +4049,32 @@
         <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="O18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
-        <v>81</v>
+        <v>183</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>81</v>
@@ -4256,13 +4092,13 @@
         <v>81</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>81</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>81</v>
@@ -4280,7 +4116,7 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>79</v>
@@ -4295,7 +4131,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4304,15 +4140,15 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4335,18 +4171,20 @@
         <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4394,7 +4232,7 @@
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>79</v>
@@ -4409,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4418,7 +4256,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4426,43 +4264,41 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4510,22 +4346,22 @@
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>145</v>
+        <v>218</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4534,26 +4370,26 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>81</v>
@@ -4562,18 +4398,20 @@
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
         <v>81</v>
@@ -4622,22 +4460,22 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4646,19 +4484,19 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4674,20 +4512,18 @@
         <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>81</v>
@@ -4724,19 +4560,19 @@
         <v>81</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4748,10 +4584,10 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4760,15 +4596,15 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4779,32 +4615,28 @@
         <v>79</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4828,13 +4660,13 @@
         <v>81</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>81</v>
@@ -4852,13 +4684,13 @@
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>81</v>
@@ -4867,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4876,15 +4708,15 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>131</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4907,19 +4739,17 @@
         <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>178</v>
+        <v>242</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>81</v>
@@ -4944,13 +4774,13 @@
         <v>81</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>81</v>
@@ -4968,7 +4798,7 @@
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>79</v>
@@ -4983,7 +4813,7 @@
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4992,7 +4822,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -5000,7 +4830,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -5008,13 +4838,13 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5023,19 +4853,19 @@
         <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>81</v>
@@ -5048,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5084,13 +4914,13 @@
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>81</v>
@@ -5099,16 +4929,16 @@
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5116,7 +4946,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5124,13 +4954,13 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5139,18 +4969,20 @@
         <v>89</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5162,7 +4994,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>201</v>
+        <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -5174,13 +5006,13 @@
         <v>81</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>81</v>
@@ -5198,7 +5030,7 @@
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>202</v>
+        <v>258</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>79</v>
@@ -5213,24 +5045,24 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5253,16 +5085,20 @@
         <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>206</v>
+        <v>269</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5310,7 +5146,7 @@
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
@@ -5325,24 +5161,24 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5359,24 +5195,26 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5424,7 +5262,7 @@
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
@@ -5439,16 +5277,16 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>218</v>
+        <v>284</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5456,7 +5294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5464,41 +5302,39 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>228</v>
+        <v>287</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>231</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5542,13 +5378,13 @@
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>81</v>
@@ -5557,24 +5393,24 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>161</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>235</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5582,35 +5418,31 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="F30" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5646,41 +5478,43 @@
         <v>81</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AB30" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AC30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5688,45 +5522,41 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>238</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5762,19 +5592,19 @@
         <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5786,29 +5616,31 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="B32" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="C32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5829,13 +5661,13 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>157</v>
+        <v>298</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>158</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>300</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5886,22 +5718,22 @@
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5916,20 +5748,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B33" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="C33" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -5941,17 +5775,15 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>134</v>
+        <v>302</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>81</v>
@@ -5988,19 +5820,19 @@
         <v>81</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -6015,7 +5847,7 @@
         <v>139</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
@@ -6030,9 +5862,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6040,7 +5872,7 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>88</v>
@@ -6058,29 +5890,29 @@
         <v>108</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>251</v>
+        <v>306</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>252</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>253</v>
+        <v>308</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="R34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -6092,13 +5924,13 @@
         <v>81</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>81</v>
@@ -6116,7 +5948,7 @@
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>79</v>
@@ -6131,7 +5963,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -6140,15 +5972,15 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6171,20 +6003,18 @@
         <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>261</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6196,7 +6026,7 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>81</v>
@@ -6208,13 +6038,13 @@
         <v>81</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>81</v>
+        <v>321</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>81</v>
@@ -6232,7 +6062,7 @@
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>79</v>
@@ -6247,7 +6077,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6256,23 +6086,23 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>88</v>
@@ -6287,18 +6117,20 @@
         <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6310,7 +6142,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>81</v>
+        <v>328</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6346,7 +6178,7 @@
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>79</v>
@@ -6361,7 +6193,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>274</v>
+        <v>211</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6370,19 +6202,19 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6401,17 +6233,15 @@
         <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>81</v>
@@ -6424,7 +6254,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6460,7 +6290,7 @@
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6475,7 +6305,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6484,26 +6314,26 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
@@ -6515,13 +6345,13 @@
         <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6536,7 +6366,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6572,13 +6402,13 @@
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
@@ -6587,7 +6417,7 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6596,26 +6426,26 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>81</v>
@@ -6627,15 +6457,17 @@
         <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
         <v>81</v>
@@ -6648,7 +6480,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6684,13 +6516,13 @@
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>293</v>
+        <v>352</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>81</v>
@@ -6699,7 +6531,7 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>294</v>
+        <v>353</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6708,19 +6540,19 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6739,18 +6571,16 @@
         <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="M40" s="2"/>
-      <c r="N40" t="s" s="2">
-        <v>299</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6798,7 +6628,7 @@
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>79</v>
@@ -6813,7 +6643,7 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6822,26 +6652,26 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>302</v>
+        <v>361</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>81</v>
+        <v>363</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -6853,20 +6683,16 @@
         <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6878,7 +6704,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -6914,13 +6740,13 @@
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>81</v>
@@ -6929,16 +6755,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>310</v>
+        <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6946,7 +6772,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6954,13 +6780,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6969,20 +6795,18 @@
         <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7006,13 +6830,13 @@
         <v>81</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
         <v>81</v>
@@ -7030,7 +6854,7 @@
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>79</v>
@@ -7045,16 +6869,16 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>321</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -7062,7 +6886,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7076,7 +6900,7 @@
         <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7085,19 +6909,17 @@
         <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>323</v>
+        <v>242</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="M43" s="2"/>
       <c r="N43" t="s" s="2">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>81</v>
@@ -7110,7 +6932,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>81</v>
@@ -7146,7 +6968,7 @@
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>79</v>
@@ -7161,24 +6983,24 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>328</v>
+        <v>247</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>330</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>331</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7195,25 +7017,23 @@
         <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>81</v>
@@ -7238,13 +7058,11 @@
         <v>81</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>81</v>
@@ -7262,7 +7080,7 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>79</v>
@@ -7277,24 +7095,24 @@
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>161</v>
+        <v>392</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7305,7 +7123,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7314,22 +7132,22 @@
         <v>81</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>341</v>
+        <v>395</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>81</v>
@@ -7378,13 +7196,13 @@
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>81</v>
@@ -7393,24 +7211,24 @@
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>347</v>
+        <v>171</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7421,7 +7239,7 @@
         <v>79</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>81</v>
@@ -7433,16 +7251,20 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>157</v>
+        <v>403</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>158</v>
+        <v>404</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7490,43 +7312,43 @@
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>160</v>
+        <v>402</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>161</v>
+        <v>408</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7545,18 +7367,20 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>134</v>
+        <v>411</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>163</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7592,19 +7416,19 @@
         <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>166</v>
+        <v>410</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7616,13 +7440,13 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>139</v>
+        <v>416</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>161</v>
+        <v>417</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -7634,13 +7458,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7661,13 +7483,13 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>353</v>
+        <v>186</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>187</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7718,22 +7540,22 @@
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7748,22 +7570,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>81</v>
@@ -7775,15 +7595,17 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>356</v>
+        <v>134</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>357</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M49" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>81</v>
@@ -7832,7 +7654,7 @@
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7847,7 +7669,7 @@
         <v>139</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7862,20 +7684,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>81</v>
@@ -7887,19 +7709,19 @@
         <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>360</v>
+        <v>422</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>137</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>363</v>
+        <v>143</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>81</v>
@@ -7912,7 +7734,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>364</v>
+        <v>81</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -7924,13 +7746,13 @@
         <v>81</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>81</v>
@@ -7948,22 +7770,22 @@
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>258</v>
+        <v>131</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -7972,15 +7794,15 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>368</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7991,7 +7813,7 @@
         <v>79</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>81</v>
@@ -8000,21 +7822,21 @@
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>108</v>
+        <v>385</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8026,7 +7848,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8038,13 +7860,13 @@
         <v>81</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>172</v>
+        <v>389</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>374</v>
+        <v>429</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>375</v>
+        <v>430</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>81</v>
@@ -8062,13 +7884,13 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>81</v>
@@ -8077,24 +7899,24 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>258</v>
+        <v>431</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>377</v>
+        <v>432</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8114,22 +7936,20 @@
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>379</v>
+        <v>434</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>264</v>
+        <v>436</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>81</v>
@@ -8142,7 +7962,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>81</v>
@@ -8178,7 +7998,7 @@
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
@@ -8193,24 +8013,24 @@
         <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8230,19 +8050,23 @@
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8254,7 +8078,7 @@
         <v>81</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>81</v>
@@ -8290,7 +8114,7 @@
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -8305,28 +8129,28 @@
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>390</v>
+        <v>255</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8342,19 +8166,21 @@
         <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>157</v>
+        <v>287</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8366,7 +8192,7 @@
         <v>81</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>396</v>
+        <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>81</v>
@@ -8402,7 +8228,7 @@
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
@@ -8417,28 +8243,28 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>398</v>
+        <v>292</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8454,21 +8280,21 @@
         <v>81</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>402</v>
+        <v>259</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8480,7 +8306,7 @@
         <v>81</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>81</v>
@@ -8492,13 +8318,13 @@
         <v>81</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>81</v>
@@ -8516,7 +8342,7 @@
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>79</v>
@@ -8531,28 +8357,28 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>407</v>
+        <v>265</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8568,19 +8394,21 @@
         <v>81</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>157</v>
+        <v>453</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>411</v>
+        <v>454</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8628,7 +8456,7 @@
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>79</v>
@@ -8637,34 +8465,34 @@
         <v>88</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8680,16 +8508,16 @@
         <v>81</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>157</v>
+        <v>242</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8704,7 +8532,7 @@
         <v>81</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>81</v>
@@ -8740,7 +8568,7 @@
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
@@ -8755,24 +8583,24 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8783,7 +8611,7 @@
         <v>79</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>81</v>
@@ -8792,21 +8620,23 @@
         <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>157</v>
+        <v>411</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="O58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8854,13 +8684,13 @@
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>81</v>
@@ -8869,24 +8699,24 @@
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8906,21 +8736,19 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>432</v>
+        <v>186</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>187</v>
       </c>
       <c r="M59" s="2"/>
-      <c r="N59" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8932,7 +8760,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -8968,7 +8796,7 @@
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>436</v>
+        <v>188</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
@@ -8980,10 +8808,10 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>301</v>
+        <v>171</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -8992,26 +8820,26 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>81</v>
@@ -9023,18 +8851,18 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>439</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9058,11 +8886,13 @@
         <v>81</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="X60" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Y60" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>81</v>
@@ -9080,74 +8910,74 @@
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>438</v>
+        <v>193</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>447</v>
+        <v>134</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>137</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
+        <v>143</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>81</v>
@@ -9196,39 +9026,39 @@
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>452</v>
+        <v>131</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9236,10 +9066,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>81</v>
@@ -9251,19 +9081,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>455</v>
+        <v>385</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>81</v>
@@ -9288,13 +9118,13 @@
         <v>81</v>
       </c>
       <c r="W62" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>81</v>
@@ -9312,13 +9142,13 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>81</v>
@@ -9327,24 +9157,24 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>161</v>
+        <v>480</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9355,7 +9185,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -9367,19 +9197,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>463</v>
+        <v>164</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>81</v>
@@ -9428,50 +9258,50 @@
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>468</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>161</v>
+        <v>488</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>81</v>
@@ -9483,15 +9313,17 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>157</v>
+        <v>492</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>158</v>
+        <v>493</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M64" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>81</v>
@@ -9528,55 +9360,55 @@
         <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="AB64" s="2"/>
       <c r="AC64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>160</v>
+        <v>490</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>161</v>
+        <v>497</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B65" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="C65" t="s" s="2">
-        <v>133</v>
+        <v>491</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9595,16 +9427,16 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>134</v>
+        <v>492</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>493</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>163</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>137</v>
+        <v>495</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9654,7 +9486,7 @@
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>166</v>
+        <v>490</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>79</v>
@@ -9666,63 +9498,59 @@
         <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>161</v>
+        <v>497</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>498</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>474</v>
+        <v>186</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9770,22 +9598,22 @@
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>476</v>
+        <v>188</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9800,13 +9628,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9825,18 +9653,18 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>478</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M67" s="2"/>
-      <c r="N67" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9860,31 +9688,31 @@
         <v>81</v>
       </c>
       <c r="W67" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>481</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AC67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>477</v>
+        <v>193</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9896,27 +9724,27 @@
         <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>483</v>
+        <v>171</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9936,21 +9764,21 @@
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>237</v>
+        <v>185</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="M68" s="2"/>
-      <c r="N68" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
         <v>81</v>
       </c>
@@ -9998,7 +9826,7 @@
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
@@ -10007,30 +9835,30 @@
         <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -10041,7 +9869,7 @@
         <v>79</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>81</v>
@@ -10050,23 +9878,21 @@
         <v>81</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10090,13 +9916,13 @@
         <v>81</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>81</v>
@@ -10114,13 +9940,13 @@
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>81</v>
@@ -10129,24 +9955,24 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -10169,18 +9995,18 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>341</v>
+        <v>516</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>496</v>
+        <v>158</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M70" s="2"/>
-      <c r="N70" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10228,7 +10054,7 @@
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
@@ -10237,30 +10063,30 @@
         <v>88</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>346</v>
+        <v>161</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>499</v>
+        <v>162</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10280,21 +10106,21 @@
         <v>81</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>313</v>
+        <v>520</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10318,13 +10144,13 @@
         <v>81</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>81</v>
@@ -10342,7 +10168,7 @@
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
@@ -10357,24 +10183,24 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>319</v>
+        <v>131</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10394,20 +10220,22 @@
         <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>213</v>
+        <v>453</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="N72" t="s" s="2">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>81</v>
@@ -10456,7 +10284,7 @@
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10465,30 +10293,30 @@
         <v>88</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>161</v>
+        <v>529</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10499,28 +10327,32 @@
         <v>79</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>206</v>
+        <v>411</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10568,13 +10400,13 @@
         <v>81</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>81</v>
@@ -10583,10 +10415,10 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
@@ -10598,9 +10430,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10611,7 +10443,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>81</v>
@@ -10623,20 +10455,16 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>463</v>
+        <v>185</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>516</v>
+        <v>186</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10684,25 +10512,25 @@
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>515</v>
+        <v>188</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>520</v>
+        <v>171</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>521</v>
+        <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
@@ -10714,20 +10542,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>81</v>
@@ -10739,15 +10567,17 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M75" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
         <v>81</v>
@@ -10796,22 +10626,22 @@
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -10826,13 +10656,13 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>133</v>
+        <v>421</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10845,24 +10675,26 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>134</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>135</v>
+        <v>422</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>163</v>
+        <v>423</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="N76" s="2"/>
+      <c r="N76" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O76" t="s" s="2">
         <v>81</v>
       </c>
@@ -10910,7 +10742,7 @@
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>166</v>
+        <v>424</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10925,7 +10757,7 @@
         <v>139</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -10940,45 +10772,43 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>134</v>
+        <v>540</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>474</v>
+        <v>541</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>475</v>
+        <v>542</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11026,39 +10856,39 @@
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -11078,23 +10908,19 @@
         <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11118,13 +10944,13 @@
         <v>81</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>113</v>
+        <v>547</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>114</v>
+        <v>548</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>81</v>
@@ -11142,7 +10968,7 @@
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>88</v>
@@ -11157,1866 +10983,22 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>531</v>
+        <v>171</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D79" s="2"/>
-      <c r="E79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P79" s="2"/>
-      <c r="Q79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B80" s="2"/>
-      <c r="C80" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="D80" s="2"/>
-      <c r="E80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P80" s="2"/>
-      <c r="Q80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AB80" s="2"/>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="D81" s="2"/>
-      <c r="E81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P81" s="2"/>
-      <c r="Q81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B82" s="2"/>
-      <c r="C82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D82" s="2"/>
-      <c r="E82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P82" s="2"/>
-      <c r="Q82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B83" s="2"/>
-      <c r="C83" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="D83" s="2"/>
-      <c r="E83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P83" s="2"/>
-      <c r="Q83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B84" s="2"/>
-      <c r="C84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P84" s="2"/>
-      <c r="Q84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="B85" s="2"/>
-      <c r="C85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P85" s="2"/>
-      <c r="Q85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="B86" s="2"/>
-      <c r="C86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D86" s="2"/>
-      <c r="E86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P86" s="2"/>
-      <c r="Q86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B87" s="2"/>
-      <c r="C87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D87" s="2"/>
-      <c r="E87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P87" s="2"/>
-      <c r="Q87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B88" s="2"/>
-      <c r="C88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D88" s="2"/>
-      <c r="E88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P88" s="2"/>
-      <c r="Q88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B89" s="2"/>
-      <c r="C89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D89" s="2"/>
-      <c r="E89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P89" s="2"/>
-      <c r="Q89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B90" s="2"/>
-      <c r="C90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D90" s="2"/>
-      <c r="E90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P90" s="2"/>
-      <c r="Q90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P91" s="2"/>
-      <c r="Q91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="B92" s="2"/>
-      <c r="C92" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P92" s="2"/>
-      <c r="Q92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B93" s="2"/>
-      <c r="C93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P93" s="2"/>
-      <c r="Q93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B94" s="2"/>
-      <c r="C94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D94" s="2"/>
-      <c r="E94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P94" s="2"/>
-      <c r="Q94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN94">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI93">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -507,7 +507,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
+    <t>[DA] cpr-nummer, som det fremgår af CPR registeret</t>
   </si>
   <si>
     <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
@@ -592,6 +592,9 @@
     <t>official</t>
   </si>
   <si>
+    <t>[DA] Officielt navn, som det fremgår af CPR registeret</t>
+  </si>
+  <si>
     <t>Patient.name.id</t>
   </si>
   <si>
@@ -947,7 +950,7 @@
 </t>
   </si>
   <si>
-    <t>Danish Core Municipality codes</t>
+    <t>[DA] Kommunekode</t>
   </si>
   <si>
     <t>Identifier holding the official identifier for a danish municipality</t>
@@ -960,7 +963,7 @@
 </t>
   </si>
   <si>
-    <t>Danish Core Regional Sub Division Codes Extension</t>
+    <t>[DA] Regionskode</t>
   </si>
   <si>
     <t>Identifier holding the official organization identifier for a danish region</t>
@@ -1575,6 +1578,9 @@
     <t>referencedSORUnit</t>
   </si>
   <si>
+    <t>[DA] Praktiserende læges SOR-id på sundhedsinstistutionsniveau</t>
+  </si>
+  <si>
     <t>Patient.generalPractitioner.id</t>
   </si>
   <si>
@@ -1627,6 +1633,9 @@
   <si>
     <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-sor-identifier}
 </t>
+  </si>
+  <si>
+    <t>An identifier intended for computation</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -3716,7 +3725,7 @@
         <v>174</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>176</v>
@@ -3806,7 +3815,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3829,13 +3838,13 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -3886,7 +3895,7 @@
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>79</v>
@@ -3918,7 +3927,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3947,7 +3956,7 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>137</v>
@@ -3988,10 +3997,10 @@
         <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>81</v>
@@ -4000,7 +4009,7 @@
         <v>151</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
@@ -4032,7 +4041,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4058,16 +4067,16 @@
         <v>108</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>81</v>
@@ -4092,13 +4101,13 @@
         <v>81</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>81</v>
@@ -4116,7 +4125,7 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>79</v>
@@ -4131,7 +4140,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4140,7 +4149,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -4148,7 +4157,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4171,19 +4180,19 @@
         <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>81</v>
@@ -4232,7 +4241,7 @@
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>79</v>
@@ -4247,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
@@ -4256,7 +4265,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4264,11 +4273,11 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4287,16 +4296,16 @@
         <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -4346,7 +4355,7 @@
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>79</v>
@@ -4361,7 +4370,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>81</v>
@@ -4370,7 +4379,7 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4378,11 +4387,11 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4401,16 +4410,16 @@
         <v>89</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4460,7 +4469,7 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
@@ -4475,7 +4484,7 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4484,7 +4493,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4492,7 +4501,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4515,13 +4524,13 @@
         <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -4572,7 +4581,7 @@
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4587,7 +4596,7 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
@@ -4596,7 +4605,7 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4604,7 +4613,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4627,13 +4636,13 @@
         <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4684,7 +4693,7 @@
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
@@ -4699,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
@@ -4708,7 +4717,7 @@
         <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4716,7 +4725,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4739,17 +4748,17 @@
         <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>81</v>
@@ -4798,7 +4807,7 @@
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>79</v>
@@ -4813,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
@@ -4822,7 +4831,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4830,7 +4839,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4853,19 +4862,19 @@
         <v>89</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>81</v>
@@ -4914,7 +4923,7 @@
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
@@ -4929,16 +4938,16 @@
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4946,7 +4955,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4972,16 +4981,16 @@
         <v>108</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>81</v>
@@ -5006,13 +5015,13 @@
         <v>81</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>81</v>
@@ -5030,7 +5039,7 @@
         <v>81</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>79</v>
@@ -5045,16 +5054,16 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5062,7 +5071,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5085,19 +5094,19 @@
         <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
         <v>81</v>
@@ -5146,7 +5155,7 @@
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
@@ -5161,24 +5170,24 @@
         <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5201,19 +5210,19 @@
         <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>81</v>
@@ -5262,7 +5271,7 @@
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
@@ -5277,7 +5286,7 @@
         <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>171</v>
@@ -5286,7 +5295,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5294,7 +5303,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5317,19 +5326,19 @@
         <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>81</v>
@@ -5378,7 +5387,7 @@
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
@@ -5393,16 +5402,16 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5410,7 +5419,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5433,13 +5442,13 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5490,7 +5499,7 @@
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
@@ -5522,7 +5531,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5551,7 +5560,7 @@
         <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>137</v>
@@ -5592,10 +5601,10 @@
         <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>81</v>
@@ -5604,7 +5613,7 @@
         <v>151</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5636,10 +5645,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>81</v>
@@ -5661,13 +5670,13 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5718,7 +5727,7 @@
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>79</v>
@@ -5750,10 +5759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>81</v>
@@ -5775,13 +5784,13 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5832,7 +5841,7 @@
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -5864,7 +5873,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5890,16 +5899,16 @@
         <v>108</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>81</v>
@@ -5912,7 +5921,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5924,13 +5933,13 @@
         <v>81</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>81</v>
@@ -5948,7 +5957,7 @@
         <v>81</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>79</v>
@@ -5963,7 +5972,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>81</v>
@@ -5972,7 +5981,7 @@
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5980,7 +5989,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6006,13 +6015,13 @@
         <v>108</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6026,7 +6035,7 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>81</v>
@@ -6038,13 +6047,13 @@
         <v>81</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>81</v>
@@ -6062,7 +6071,7 @@
         <v>81</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>79</v>
@@ -6077,7 +6086,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>81</v>
@@ -6086,7 +6095,7 @@
         <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6094,7 +6103,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6117,19 +6126,19 @@
         <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>81</v>
@@ -6142,7 +6151,7 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>81</v>
@@ -6178,7 +6187,7 @@
         <v>81</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>79</v>
@@ -6193,7 +6202,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>81</v>
@@ -6202,7 +6211,7 @@
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6210,7 +6219,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6233,13 +6242,13 @@
         <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -6254,7 +6263,7 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>81</v>
@@ -6290,7 +6299,7 @@
         <v>81</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6305,7 +6314,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>81</v>
@@ -6314,7 +6323,7 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6322,11 +6331,11 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6345,13 +6354,13 @@
         <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6366,7 +6375,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6402,7 +6411,7 @@
         <v>81</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>79</v>
@@ -6417,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6426,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6434,11 +6443,11 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6457,16 +6466,16 @@
         <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6480,7 +6489,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6516,7 +6525,7 @@
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>79</v>
@@ -6531,7 +6540,7 @@
         <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6540,7 +6549,7 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6548,11 +6557,11 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6571,13 +6580,13 @@
         <v>89</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6628,7 +6637,7 @@
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>79</v>
@@ -6643,7 +6652,7 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
@@ -6652,7 +6661,7 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6660,11 +6669,11 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6683,13 +6692,13 @@
         <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6704,7 +6713,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -6740,7 +6749,7 @@
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>79</v>
@@ -6755,7 +6764,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -6764,7 +6773,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6772,7 +6781,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6795,16 +6804,16 @@
         <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6854,7 +6863,7 @@
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>79</v>
@@ -6869,7 +6878,7 @@
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -6878,7 +6887,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6886,7 +6895,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6909,17 +6918,17 @@
         <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>81</v>
@@ -6932,7 +6941,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>81</v>
@@ -6968,7 +6977,7 @@
         <v>81</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>79</v>
@@ -6983,7 +6992,7 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6992,7 +7001,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7000,7 +7009,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7023,17 +7032,17 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>81</v>
@@ -7058,11 +7067,11 @@
         <v>81</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>81</v>
@@ -7080,7 +7089,7 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>79</v>
@@ -7095,16 +7104,16 @@
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7112,7 +7121,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7135,19 +7144,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>81</v>
@@ -7196,7 +7205,7 @@
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
@@ -7211,7 +7220,7 @@
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>171</v>
@@ -7220,7 +7229,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7228,7 +7237,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7251,19 +7260,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>81</v>
@@ -7312,7 +7321,7 @@
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
@@ -7327,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>171</v>
@@ -7336,7 +7345,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7344,7 +7353,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7367,19 +7376,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>81</v>
@@ -7428,7 +7437,7 @@
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7440,10 +7449,10 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>171</v>
@@ -7460,7 +7469,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7483,13 +7492,13 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7540,7 +7549,7 @@
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>79</v>
@@ -7572,7 +7581,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7601,7 +7610,7 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M49" t="s" s="2">
         <v>137</v>
@@ -7654,7 +7663,7 @@
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7686,11 +7695,11 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7712,10 +7721,10 @@
         <v>134</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>137</v>
@@ -7770,7 +7779,7 @@
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
@@ -7802,7 +7811,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7825,17 +7834,17 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>81</v>
@@ -7860,13 +7869,13 @@
         <v>81</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>81</v>
@@ -7884,7 +7893,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
@@ -7899,7 +7908,7 @@
         <v>100</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>171</v>
@@ -7908,7 +7917,7 @@
         <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7916,7 +7925,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7942,14 +7951,14 @@
         <v>174</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>81</v>
@@ -7998,7 +8007,7 @@
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
@@ -8022,7 +8031,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8030,7 +8039,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8053,19 +8062,19 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>81</v>
@@ -8114,7 +8123,7 @@
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -8129,7 +8138,7 @@
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>171</v>
@@ -8138,7 +8147,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8146,7 +8155,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8169,17 +8178,17 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>81</v>
@@ -8228,7 +8237,7 @@
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
@@ -8243,7 +8252,7 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>171</v>
@@ -8252,7 +8261,7 @@
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8260,7 +8269,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8286,14 +8295,14 @@
         <v>108</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>81</v>
@@ -8318,13 +8327,13 @@
         <v>81</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>81</v>
@@ -8342,7 +8351,7 @@
         <v>81</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>79</v>
@@ -8357,7 +8366,7 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>171</v>
@@ -8366,7 +8375,7 @@
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8374,7 +8383,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8397,17 +8406,17 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>81</v>
@@ -8456,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>79</v>
@@ -8465,13 +8474,13 @@
         <v>88</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>171</v>
@@ -8480,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8488,7 +8497,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8511,13 +8520,13 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8568,7 +8577,7 @@
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
@@ -8583,7 +8592,7 @@
         <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>171</v>
@@ -8600,7 +8609,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8623,19 +8632,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>81</v>
@@ -8684,7 +8693,7 @@
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
@@ -8699,10 +8708,10 @@
         <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -8716,7 +8725,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8739,13 +8748,13 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8796,7 +8805,7 @@
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
@@ -8828,7 +8837,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8857,7 +8866,7 @@
         <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M60" t="s" s="2">
         <v>137</v>
@@ -8910,7 +8919,7 @@
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
@@ -8942,11 +8951,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8968,10 +8977,10 @@
         <v>134</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>137</v>
@@ -9026,7 +9035,7 @@
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
@@ -9058,7 +9067,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9081,19 +9090,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>81</v>
@@ -9142,7 +9151,7 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>88</v>
@@ -9157,16 +9166,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9174,7 +9183,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9200,16 +9209,16 @@
         <v>164</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>81</v>
@@ -9258,7 +9267,7 @@
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
@@ -9273,16 +9282,16 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9290,11 +9299,11 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9313,16 +9322,16 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9360,7 +9369,7 @@
         <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AB64" s="2"/>
       <c r="AC64" t="s" s="2">
@@ -9370,7 +9379,7 @@
         <v>151</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
@@ -9385,7 +9394,7 @@
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>171</v>
@@ -9394,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9402,13 +9411,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9427,16 +9436,16 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9486,7 +9495,7 @@
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>79</v>
@@ -9501,7 +9510,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>171</v>
@@ -9510,7 +9519,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9518,7 +9527,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9541,13 +9550,13 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9598,7 +9607,7 @@
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
@@ -9630,7 +9639,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9659,7 +9668,7 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>137</v>
@@ -9700,10 +9709,10 @@
         <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AC67" t="s" s="2">
         <v>81</v>
@@ -9712,7 +9721,7 @@
         <v>151</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9744,7 +9753,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9767,16 +9776,16 @@
         <v>89</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
@@ -9826,7 +9835,7 @@
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>79</v>
@@ -9835,7 +9844,7 @@
         <v>88</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>100</v>
@@ -9858,7 +9867,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9884,13 +9893,13 @@
         <v>102</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
@@ -9916,13 +9925,13 @@
         <v>81</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>81</v>
@@ -9940,7 +9949,7 @@
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
@@ -9972,7 +9981,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9995,16 +10004,16 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>158</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>159</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10054,7 +10063,7 @@
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
@@ -10086,7 +10095,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10109,16 +10118,16 @@
         <v>89</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10168,7 +10177,7 @@
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
@@ -10200,7 +10209,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10223,19 +10232,19 @@
         <v>89</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>81</v>
@@ -10284,7 +10293,7 @@
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
@@ -10299,10 +10308,10 @@
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
@@ -10316,7 +10325,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10339,19 +10348,19 @@
         <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>81</v>
@@ -10400,7 +10409,7 @@
         <v>81</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>79</v>
@@ -10415,7 +10424,7 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>171</v>
@@ -10432,7 +10441,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10455,13 +10464,13 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10512,7 +10521,7 @@
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
@@ -10544,7 +10553,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10573,7 +10582,7 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>137</v>
@@ -10626,7 +10635,7 @@
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
@@ -10658,11 +10667,11 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10684,10 +10693,10 @@
         <v>134</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>137</v>
@@ -10742,7 +10751,7 @@
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10774,7 +10783,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10797,16 +10806,16 @@
         <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
@@ -10856,7 +10865,7 @@
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>88</v>
@@ -10880,7 +10889,7 @@
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -10888,7 +10897,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10914,10 +10923,10 @@
         <v>108</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10944,31 +10953,31 @@
         <v>81</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>88</v>
@@ -10983,7 +10992,7 @@
         <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>171</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2859" uniqueCount="552">
   <si>
     <t>Property</t>
   </si>
@@ -266,10 +266,6 @@
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}marital-status-unknown-usage:Status in maritalStatus is unknown in a danish context. Consider mapping the value to UNK {maritalStatus.coding.where(code = 'P' and system = 'http://terminology.hl7.org/CodeSystem/v3-MaritalStatus').empty() or maritalStatus.coding.where(code = 'A' and system = 'http://terminology.hl7.org/CodeSystem/v3-MaritalStatus').empty()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -2305,13 +2301,13 @@
         <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AJ2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>81</v>
@@ -2325,7 +2321,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2336,28 +2332,28 @@
         <v>79</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I3" t="s" s="2">
+      <c r="J3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s" s="2">
@@ -2407,13 +2403,13 @@
         <v>81</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>81</v>
@@ -2439,7 +2435,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2450,25 +2446,25 @@
         <v>79</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I4" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -2519,19 +2515,19 @@
         <v>81</v>
       </c>
       <c r="AE4" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -2551,7 +2547,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2562,28 +2558,28 @@
         <v>79</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" t="s" s="2">
@@ -2633,19 +2629,19 @@
         <v>81</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>81</v>
@@ -2665,7 +2661,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2676,7 +2672,7 @@
         <v>79</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>81</v>
@@ -2688,16 +2684,16 @@
         <v>81</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
@@ -2723,43 +2719,43 @@
         <v>81</v>
       </c>
       <c r="W6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="X6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="Y6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AF6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>81</v>
@@ -2779,18 +2775,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>81</v>
@@ -2802,16 +2798,16 @@
         <v>81</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="L7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
@@ -2861,22 +2857,22 @@
         <v>81</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -2893,11 +2889,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2916,16 +2912,16 @@
         <v>81</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" t="s" s="2">
@@ -2975,7 +2971,7 @@
         <v>81</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF8" t="s" s="2">
         <v>79</v>
@@ -2990,7 +2986,7 @@
         <v>81</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>81</v>
@@ -3007,11 +3003,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -3030,16 +3026,16 @@
         <v>81</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
@@ -3089,7 +3085,7 @@
         <v>81</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>79</v>
@@ -3101,10 +3097,10 @@
         <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3121,11 +3117,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -3138,25 +3134,25 @@
         <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
         <v>81</v>
@@ -3205,7 +3201,7 @@
         <v>81</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>79</v>
@@ -3217,10 +3213,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3237,7 +3233,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -3245,7 +3241,7 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>80</v>
@@ -3257,20 +3253,20 @@
         <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="K11" t="s" s="2">
+      <c r="L11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O11" t="s" s="2">
         <v>81</v>
@@ -3307,17 +3303,17 @@
         <v>81</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>79</v>
@@ -3329,19 +3325,19 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>81</v>
@@ -3349,10 +3345,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>81</v>
@@ -3362,7 +3358,7 @@
         <v>79</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3374,17 +3370,17 @@
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O12" t="s" s="2">
         <v>81</v>
@@ -3433,7 +3429,7 @@
         <v>81</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>79</v>
@@ -3442,22 +3438,22 @@
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AI12" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
+      <c r="AK12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>81</v>
@@ -3465,7 +3461,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -3476,103 +3472,103 @@
         <v>79</v>
       </c>
       <c r="F13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="L13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="O13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="P13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="P13" t="s" s="2">
+      <c r="Q13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="Q13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
+      <c r="AK13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>81</v>
@@ -3583,7 +3579,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3603,22 +3599,22 @@
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>81</v>
@@ -3655,17 +3651,17 @@
         <v>81</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB14" s="2"/>
       <c r="AC14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>79</v>
@@ -3677,19 +3673,19 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>81</v>
@@ -3697,10 +3693,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>81</v>
@@ -3710,31 +3706,31 @@
         <v>79</v>
       </c>
       <c r="F15" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>81</v>
@@ -3783,7 +3779,7 @@
         <v>81</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>79</v>
@@ -3795,19 +3791,19 @@
         <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3815,7 +3811,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3826,7 +3822,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>81</v>
@@ -3838,13 +3834,13 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K16" t="s" s="2">
+      <c r="L16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -3895,13 +3891,13 @@
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>81</v>
@@ -3910,7 +3906,7 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
@@ -3927,11 +3923,11 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3950,16 +3946,16 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -3997,19 +3993,19 @@
         <v>81</v>
       </c>
       <c r="AA17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AB17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AB17" t="s" s="2">
+      <c r="AC17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>79</v>
@@ -4021,10 +4017,10 @@
         <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>81</v>
@@ -4041,7 +4037,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -4049,41 +4045,41 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="F18" t="s" s="2">
+      <c r="I18" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J18" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>81</v>
@@ -4101,55 +4097,55 @@
         <v>81</v>
       </c>
       <c r="W18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="X18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="X18" t="s" s="2">
+      <c r="Y18" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AF18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
+      <c r="AK18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -4157,7 +4153,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -4168,31 +4164,31 @@
         <v>79</v>
       </c>
       <c r="F19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J19" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>81</v>
@@ -4241,31 +4237,31 @@
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AF19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
+      <c r="AK19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4273,39 +4269,39 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="F20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
@@ -4355,31 +4351,31 @@
         <v>81</v>
       </c>
       <c r="AE20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AF20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
+      <c r="AK20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -4387,11 +4383,11 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4407,19 +4403,19 @@
         <v>81</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4469,7 +4465,7 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>79</v>
@@ -4481,19 +4477,19 @@
         <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4501,7 +4497,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4521,16 +4517,16 @@
         <v>81</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -4581,7 +4577,7 @@
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>79</v>
@@ -4593,19 +4589,19 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4613,7 +4609,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4633,16 +4629,16 @@
         <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4693,7 +4689,7 @@
         <v>81</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>79</v>
@@ -4705,19 +4701,19 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4725,7 +4721,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4736,29 +4732,29 @@
         <v>79</v>
       </c>
       <c r="F24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>81</v>
@@ -4807,31 +4803,31 @@
         <v>81</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AF24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4839,7 +4835,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4859,22 +4855,22 @@
         <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>81</v>
@@ -4923,7 +4919,7 @@
         <v>81</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>79</v>
@@ -4935,19 +4931,19 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4955,7 +4951,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4966,31 +4962,31 @@
         <v>79</v>
       </c>
       <c r="F26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J26" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
         <v>81</v>
@@ -5015,55 +5011,55 @@
         <v>81</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5071,7 +5067,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5082,31 +5078,31 @@
         <v>79</v>
       </c>
       <c r="F27" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="K27" t="s" s="2">
+      <c r="L27" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
         <v>81</v>
@@ -5155,39 +5151,39 @@
         <v>81</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5198,31 +5194,31 @@
         <v>79</v>
       </c>
       <c r="F28" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H28" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="L28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>81</v>
@@ -5271,31 +5267,31 @@
         <v>81</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5303,7 +5299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5323,22 +5319,22 @@
         <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="K29" t="s" s="2">
+      <c r="L29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>81</v>
@@ -5387,7 +5383,7 @@
         <v>81</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>79</v>
@@ -5399,19 +5395,19 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AK29" t="s" s="2">
+      <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5419,7 +5415,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5430,7 +5426,7 @@
         <v>79</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
@@ -5442,13 +5438,13 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="L30" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5499,13 +5495,13 @@
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>81</v>
@@ -5514,7 +5510,7 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
@@ -5531,11 +5527,11 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5554,16 +5550,16 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K31" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -5601,19 +5597,19 @@
         <v>81</v>
       </c>
       <c r="AA31" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AB31" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AB31" t="s" s="2">
+      <c r="AC31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>79</v>
@@ -5625,10 +5621,10 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
@@ -5645,10 +5641,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>81</v>
@@ -5658,7 +5654,7 @@
         <v>79</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>81</v>
@@ -5670,13 +5666,13 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="K32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="K32" t="s" s="2">
+      <c r="L32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5727,7 +5723,7 @@
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>79</v>
@@ -5739,7 +5735,7 @@
         <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>81</v>
@@ -5759,10 +5755,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>81</v>
@@ -5772,7 +5768,7 @@
         <v>79</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -5784,13 +5780,13 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="K33" t="s" s="2">
+      <c r="L33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5841,7 +5837,7 @@
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>79</v>
@@ -5853,7 +5849,7 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>81</v>
@@ -5873,7 +5869,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5884,31 +5880,31 @@
         <v>79</v>
       </c>
       <c r="F34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="I34" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>81</v>
@@ -5921,67 +5917,67 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="X34" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="T34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="X34" t="s" s="2">
+      <c r="Y34" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE34" t="s" s="2">
+      <c r="AF34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5989,7 +5985,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6000,28 +5996,28 @@
         <v>79</v>
       </c>
       <c r="F35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J35" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6035,67 +6031,67 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="X35" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="T35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="X35" t="s" s="2">
+      <c r="Y35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE35" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE35" t="s" s="2">
+      <c r="AF35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6103,7 +6099,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6114,31 +6110,31 @@
         <v>79</v>
       </c>
       <c r="F36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="N36" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>81</v>
@@ -6151,67 +6147,67 @@
         <v>81</v>
       </c>
       <c r="S36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="T36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE36" t="s" s="2">
+      <c r="AF36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6219,7 +6215,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6239,16 +6235,16 @@
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -6263,43 +6259,43 @@
         <v>81</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>79</v>
@@ -6311,19 +6307,19 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -6331,36 +6327,36 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J38" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6375,67 +6371,67 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="T38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE38" t="s" s="2">
+      <c r="AF38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AF38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
+      <c r="AK38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
@@ -6443,39 +6439,39 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J39" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6489,67 +6485,67 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="T39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE39" t="s" s="2">
+      <c r="AF39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AF39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
+      <c r="AK39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6557,36 +6553,36 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J40" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6637,31 +6633,31 @@
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AF40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AK40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6669,36 +6665,36 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="F41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J41" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -6713,67 +6709,67 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="T41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
+      <c r="AF41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AF41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AK41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6781,7 +6777,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6792,28 +6788,28 @@
         <v>79</v>
       </c>
       <c r="F42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6863,31 +6859,31 @@
         <v>81</v>
       </c>
       <c r="AE42" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AF42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
+      <c r="AK42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6895,7 +6891,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6906,29 +6902,29 @@
         <v>79</v>
       </c>
       <c r="F43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I43" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J43" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
         <v>81</v>
@@ -6941,67 +6937,67 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="T43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE43" t="s" s="2">
+      <c r="AF43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -7009,7 +7005,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7020,7 +7016,7 @@
         <v>79</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>81</v>
@@ -7032,17 +7028,17 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="K44" t="s" s="2">
+      <c r="L44" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>81</v>
@@ -7067,53 +7063,53 @@
         <v>81</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
+      <c r="AK44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AK44" t="s" s="2">
+      <c r="AL44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7121,7 +7117,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7132,7 +7128,7 @@
         <v>79</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7144,19 +7140,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="K45" t="s" s="2">
+      <c r="L45" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>81</v>
@@ -7205,31 +7201,31 @@
         <v>81</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7237,7 +7233,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7260,19 +7256,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K46" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K46" t="s" s="2">
+      <c r="L46" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>81</v>
@@ -7321,7 +7317,7 @@
         <v>81</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>79</v>
@@ -7333,19 +7329,19 @@
         <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7353,7 +7349,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7376,19 +7372,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="K47" t="s" s="2">
+      <c r="L47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>81</v>
@@ -7437,7 +7433,7 @@
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>79</v>
@@ -7449,13 +7445,13 @@
         <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AK47" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>81</v>
@@ -7469,7 +7465,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7480,7 +7476,7 @@
         <v>79</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>81</v>
@@ -7492,13 +7488,13 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7549,13 +7545,13 @@
         <v>81</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>81</v>
@@ -7564,7 +7560,7 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
@@ -7581,11 +7577,11 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7604,16 +7600,16 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K49" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K49" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L49" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
@@ -7663,7 +7659,7 @@
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>79</v>
@@ -7675,10 +7671,10 @@
         <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>81</v>
@@ -7695,11 +7691,11 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7712,25 +7708,25 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="M50" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>81</v>
@@ -7779,7 +7775,7 @@
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>79</v>
@@ -7791,10 +7787,10 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>81</v>
@@ -7811,7 +7807,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7834,17 +7830,17 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="O51" t="s" s="2">
         <v>81</v>
@@ -7869,14 +7865,14 @@
         <v>81</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="Z51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7893,7 +7889,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>79</v>
@@ -7905,19 +7901,19 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
@@ -7925,7 +7921,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7936,7 +7932,7 @@
         <v>79</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>81</v>
@@ -7948,17 +7944,17 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>81</v>
@@ -8007,31 +8003,31 @@
         <v>81</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -8039,7 +8035,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8062,19 +8058,19 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="N53" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>81</v>
@@ -8123,7 +8119,7 @@
         <v>81</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>79</v>
@@ -8135,19 +8131,19 @@
         <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -8155,7 +8151,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8166,7 +8162,7 @@
         <v>79</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>81</v>
@@ -8178,17 +8174,17 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>81</v>
@@ -8237,31 +8233,31 @@
         <v>81</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -8269,7 +8265,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8280,7 +8276,7 @@
         <v>79</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>81</v>
@@ -8292,17 +8288,17 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>81</v>
@@ -8327,55 +8323,55 @@
         <v>81</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Z55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -8383,7 +8379,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8394,7 +8390,7 @@
         <v>79</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>81</v>
@@ -8406,17 +8402,17 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="K56" t="s" s="2">
+      <c r="L56" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>81</v>
@@ -8465,31 +8461,31 @@
         <v>81</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH56" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AI56" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
+      <c r="AK56" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8497,7 +8493,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8508,7 +8504,7 @@
         <v>79</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>81</v>
@@ -8520,13 +8516,13 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8577,25 +8573,25 @@
         <v>81</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>81</v>
@@ -8609,7 +8605,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8632,19 +8628,19 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>81</v>
@@ -8693,7 +8689,7 @@
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>79</v>
@@ -8705,13 +8701,13 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AK58" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8721,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8736,7 +8732,7 @@
         <v>79</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>81</v>
@@ -8748,13 +8744,13 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K59" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K59" t="s" s="2">
+      <c r="L59" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8805,13 +8801,13 @@
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>81</v>
@@ -8820,7 +8816,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -8837,11 +8833,11 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8860,16 +8856,16 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K60" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L60" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
@@ -8919,7 +8915,7 @@
         <v>81</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>79</v>
@@ -8931,10 +8927,10 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>81</v>
@@ -8951,11 +8947,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8968,25 +8964,25 @@
         <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="M61" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>81</v>
@@ -9035,7 +9031,7 @@
         <v>81</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>79</v>
@@ -9047,10 +9043,10 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9067,7 +9063,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9075,10 +9071,10 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>81</v>
@@ -9090,19 +9086,19 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>81</v>
@@ -9127,14 +9123,14 @@
         <v>81</v>
       </c>
       <c r="W62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="X62" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="X62" t="s" s="2">
+      <c r="Y62" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y62" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="Z62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9151,31 +9147,31 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AK62" t="s" s="2">
+      <c r="AL62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9183,7 +9179,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9194,7 +9190,7 @@
         <v>79</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>81</v>
@@ -9206,19 +9202,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>81</v>
@@ -9267,31 +9263,31 @@
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AK63" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AK63" t="s" s="2">
+      <c r="AL63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9299,11 +9295,11 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9322,16 +9318,16 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="K64" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="K64" t="s" s="2">
+      <c r="L64" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9369,17 +9365,17 @@
         <v>81</v>
       </c>
       <c r="AA64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AB64" s="2"/>
       <c r="AC64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AD64" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>79</v>
@@ -9391,19 +9387,19 @@
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9411,13 +9407,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9436,16 +9432,16 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9495,7 +9491,7 @@
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>79</v>
@@ -9507,19 +9503,19 @@
         <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -9527,7 +9523,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9538,7 +9534,7 @@
         <v>79</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>81</v>
@@ -9550,13 +9546,13 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K66" t="s" s="2">
+      <c r="L66" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9607,13 +9603,13 @@
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>81</v>
@@ -9622,7 +9618,7 @@
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>81</v>
@@ -9639,11 +9635,11 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9662,16 +9658,16 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K67" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L67" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
@@ -9709,19 +9705,19 @@
         <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AB67" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AB67" t="s" s="2">
+      <c r="AC67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AE67" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>79</v>
@@ -9733,10 +9729,10 @@
         <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
@@ -9753,7 +9749,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9764,28 +9760,28 @@
         <v>79</v>
       </c>
       <c r="F68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J68" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
@@ -9835,22 +9831,22 @@
         <v>81</v>
       </c>
       <c r="AE68" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH68" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AF68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>509</v>
-      </c>
       <c r="AI68" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
@@ -9867,7 +9863,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9878,28 +9874,28 @@
         <v>79</v>
       </c>
       <c r="F69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I69" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J69" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
@@ -9925,46 +9921,46 @@
         <v>81</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="X69" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="Y69" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="Y69" t="s" s="2">
+      <c r="Z69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE69" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AF69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
@@ -9981,7 +9977,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9992,7 +9988,7 @@
         <v>79</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>81</v>
@@ -10004,16 +10000,16 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="K70" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="K70" t="s" s="2">
+      <c r="L70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10063,31 +10059,31 @@
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH70" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AI70" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10095,7 +10091,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10106,28 +10102,28 @@
         <v>79</v>
       </c>
       <c r="F71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J71" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10177,22 +10173,22 @@
         <v>81</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10209,7 +10205,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10220,31 +10216,31 @@
         <v>79</v>
       </c>
       <c r="F72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I72" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J72" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>81</v>
@@ -10293,25 +10289,25 @@
         <v>81</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
@@ -10325,7 +10321,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10342,25 +10338,25 @@
         <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>81</v>
@@ -10409,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>79</v>
@@ -10421,13 +10417,13 @@
         <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
@@ -10441,7 +10437,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10452,7 +10448,7 @@
         <v>79</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>81</v>
@@ -10464,13 +10460,13 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="K74" t="s" s="2">
+      <c r="L74" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10521,13 +10517,13 @@
         <v>81</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>81</v>
@@ -10536,7 +10532,7 @@
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>81</v>
@@ -10553,11 +10549,11 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10576,16 +10572,16 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="K75" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="K75" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="L75" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
@@ -10635,7 +10631,7 @@
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>79</v>
@@ -10647,10 +10643,10 @@
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
@@ -10667,11 +10663,11 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10684,25 +10680,25 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L76" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="M76" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>81</v>
@@ -10751,7 +10747,7 @@
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>79</v>
@@ -10763,10 +10759,10 @@
         <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
@@ -10783,7 +10779,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10791,31 +10787,31 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="F77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="K77" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="K77" t="s" s="2">
+      <c r="L77" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
@@ -10865,31 +10861,31 @@
         <v>81</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -10897,7 +10893,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10905,28 +10901,28 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I78" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="F78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="J78" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -10953,49 +10949,49 @@
         <v>81</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="X78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Y78" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="Y78" t="s" s="2">
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="AK78" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$94</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="635">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
+    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -488,6 +491,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pat-1:At least one of Patient.identifier.system or Patient.identifier.type or Patient.identifier.assigner SHALL be present {system.exists() or type.exists() or assigner.exists()}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -498,6 +505,203 @@
   </si>
   <si>
     <t>PID-3</t>
+  </si>
+  <si>
+    <t>Patient.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Patient.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Patient.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique within the system.</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Patient.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>Patient.identifier:cpr</t>
@@ -524,6 +728,30 @@
   </si>
   <si>
     <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.system</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:cpr.assigner</t>
   </si>
   <si>
     <t>Patient.active</t>
@@ -551,10 +779,11 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pat-4:If Patient.link is present, then Patient.active SHALL be present {link.exists() implies active.exists()}</t>
+  </si>
+  <si>
     <t>statusCode</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>FiveWs.status</t>
@@ -583,6 +812,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ipa-pat-2:Either Patient.name.given and/or Patient.name.family and/or Patient.name.text SHALL be present or a Data Absent Reason Extension SHALL be present. {(family.exists() or given.exists() or text.exists()) xor extension.where(url='http://hl7.org/fhir/StructureDefinition/data-absent-reason').exists()}ipa-pat-3:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -607,38 +840,12 @@
     <t>Patient.name.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Patient.name:official.extension</t>
   </si>
   <si>
     <t>Patient.name.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Patient.name:official.use</t>
   </si>
   <si>
@@ -655,9 +862,6 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -804,10 +1008,6 @@
   </si>
   <si>
     <t>Patient.name.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Time period when name was/is in use</t>
@@ -1255,10 +1455,6 @@
     <t>Patient.maritalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Marital (civil) status of a patient</t>
   </si>
   <si>
@@ -1266,9 +1462,6 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.dk/fhir/core/ValueSet/dk-marital-status</t>
@@ -1469,10 +1662,6 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
     <t>Organization that is associated with the contact</t>
   </si>
   <si>
@@ -1755,6 +1944,10 @@
     <t>There are multiple use cases:   
 * Duplicate patient records due to the clerical errors associated with the difficulties of identifying humans consistently, and 
 * Distribution of patient information across multiple servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ipa-pat-4
+</t>
   </si>
   <si>
     <t>outboundLink</t>
@@ -1929,6 +2122,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2102,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.453125" customWidth="true" bestFit="true"/>
@@ -2129,7 +2337,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.2734375" customWidth="true" bestFit="true"/>
@@ -2272,7 +2480,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2387,7 +2595,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2504,7 +2712,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2619,7 +2827,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2736,7 +2944,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2853,7 +3061,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2970,7 +3178,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3087,7 +3295,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3204,7 +3412,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3323,7 +3531,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3342,7 +3550,7 @@
         <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>81</v>
@@ -3420,34 +3628,32 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C12" t="s" s="2">
         <v>157</v>
       </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3477,9 +3683,7 @@
         <v>160</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3527,19 +3731,19 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>162</v>
@@ -3551,139 +3755,135 @@
         <v>81</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AO12" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="AC13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>174</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3694,31 +3894,31 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3743,35 +3943,37 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>81</v>
@@ -3780,31 +3982,29 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3825,19 +4025,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3862,13 +4062,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3886,13 +4086,13 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -3901,27 +4101,27 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3941,10 +4141,10 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>190</v>
@@ -3952,8 +4152,12 @@
       <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3965,7 +4169,7 @@
         <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>81</v>
@@ -4001,7 +4205,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4013,10 +4217,10 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -4025,50 +4229,50 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4082,7 +4286,7 @@
         <v>81</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>81</v>
@@ -4106,34 +4310,34 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
@@ -4142,18 +4346,18 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4161,7 +4365,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
@@ -4170,32 +4374,28 @@
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>81</v>
@@ -4213,13 +4413,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4237,7 +4437,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4252,7 +4452,7 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -4261,18 +4461,18 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4295,20 +4495,18 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4356,7 +4554,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4371,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -4380,52 +4578,54 @@
         <v>81</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="O20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4473,19 +4673,19 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>227</v>
@@ -4503,23 +4703,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4528,20 +4728,18 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4590,22 +4788,22 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>161</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4614,22 +4812,22 @@
         <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4645,18 +4843,20 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4693,19 +4893,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4717,10 +4917,10 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
@@ -4729,18 +4929,18 @@
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>81</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4751,28 +4951,32 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -4796,13 +5000,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -4820,13 +5024,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>176</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4835,7 +5039,7 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -4844,18 +5048,18 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>178</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4878,17 +5082,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4913,13 +5119,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -4937,7 +5143,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4952,7 +5158,7 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4961,18 +5167,18 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>189</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4983,7 +5189,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -4995,19 +5201,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5020,7 +5226,7 @@
         <v>81</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>81</v>
@@ -5056,13 +5262,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>195</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5071,27 +5277,27 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>267</v>
+        <v>196</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5099,13 +5305,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -5114,20 +5320,18 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>200</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5139,7 +5343,7 @@
         <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>81</v>
@@ -5151,13 +5355,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5175,7 +5379,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5190,27 +5394,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5233,20 +5437,16 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5294,7 +5494,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5309,27 +5509,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5346,26 +5546,24 @@
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5413,7 +5611,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>218</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5428,27 +5626,27 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>220</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5459,36 +5657,38 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>241</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q29" s="2"/>
+      <c r="Q29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="R29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5532,42 +5732,42 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>162</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5578,28 +5778,32 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5635,88 +5839,90 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5752,19 +5958,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5776,34 +5982,32 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>254</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>256</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5824,13 +6028,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>158</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>159</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>160</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5881,22 +6085,22 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5911,25 +6115,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5941,15 +6143,17 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>316</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5986,19 +6190,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6013,7 +6217,7 @@
         <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6028,12 +6232,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6041,7 +6245,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -6059,29 +6263,29 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>268</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>81</v>
@@ -6093,13 +6297,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>325</v>
+        <v>271</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6117,7 +6321,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6132,7 +6336,7 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6141,18 +6345,18 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>328</v>
+        <v>275</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6175,18 +6379,20 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6198,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>333</v>
+        <v>81</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>81</v>
@@ -6210,13 +6416,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6234,7 +6440,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6249,7 +6455,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6258,26 +6464,26 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -6292,20 +6498,18 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6317,7 +6521,7 @@
         <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>81</v>
@@ -6353,7 +6557,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6368,7 +6572,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>218</v>
+        <v>292</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -6377,22 +6581,22 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>81</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6411,15 +6615,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6432,7 +6638,7 @@
         <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>348</v>
+        <v>81</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>81</v>
@@ -6468,7 +6674,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6483,7 +6689,7 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6492,29 +6698,29 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6526,13 +6732,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6547,7 +6753,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>356</v>
+        <v>81</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6583,13 +6789,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6598,7 +6804,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6607,29 +6813,29 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6641,17 +6847,15 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6664,7 +6868,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -6700,13 +6904,13 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -6715,7 +6919,7 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6724,22 +6928,22 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>316</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6758,16 +6962,18 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6815,7 +7021,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6830,7 +7036,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -6839,29 +7045,29 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6873,16 +7079,20 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6894,7 +7104,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -6930,13 +7140,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -6945,27 +7155,27 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>382</v>
+        <v>331</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6979,7 +7189,7 @@
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -6988,18 +7198,20 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7023,13 +7235,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7047,7 +7259,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7062,27 +7274,27 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>343</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7096,7 +7308,7 @@
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7105,17 +7317,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>345</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7128,7 +7342,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7164,7 +7378,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7179,27 +7393,27 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>81</v>
+        <v>351</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7216,23 +7430,25 @@
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>399</v>
+        <v>355</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>402</v>
+        <v>359</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7257,11 +7473,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7279,7 +7497,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7294,27 +7512,27 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>406</v>
+        <v>162</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7325,7 +7543,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7334,22 +7552,22 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>413</v>
+        <v>367</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7398,13 +7616,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7413,27 +7631,27 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>172</v>
+        <v>369</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7444,7 +7662,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7456,20 +7674,16 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>158</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>159</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7517,46 +7731,46 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>161</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>422</v>
+        <v>162</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7575,20 +7789,18 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>425</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>426</v>
+        <v>135</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>427</v>
+        <v>164</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7624,19 +7836,19 @@
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>167</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7648,13 +7860,13 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>430</v>
+        <v>139</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>431</v>
+        <v>162</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7666,14 +7878,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7694,13 +7908,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>190</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
+        <v>377</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7751,22 +7965,22 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
@@ -7781,23 +7995,25 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7809,17 +8025,15 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>135</v>
+        <v>381</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -7868,7 +8082,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7883,7 +8097,7 @@
         <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -7898,23 +8112,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7926,19 +8140,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>137</v>
+        <v>386</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>143</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7951,7 +8165,7 @@
         <v>81</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>81</v>
+        <v>388</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>81</v>
@@ -7963,13 +8177,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7987,22 +8201,22 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>438</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8011,18 +8225,18 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8033,7 +8247,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8042,21 +8256,21 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8068,7 +8282,7 @@
         <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>81</v>
+        <v>397</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>81</v>
@@ -8080,13 +8294,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>403</v>
+        <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8104,13 +8318,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -8119,27 +8333,27 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>445</v>
+        <v>274</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8159,20 +8373,22 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>450</v>
+        <v>281</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8185,7 +8401,7 @@
         <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>81</v>
@@ -8221,7 +8437,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8236,27 +8452,27 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>181</v>
+        <v>283</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>451</v>
+        <v>408</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>409</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8276,23 +8492,19 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8304,7 +8516,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8340,7 +8552,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8355,31 +8567,31 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>267</v>
+        <v>414</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>456</v>
+        <v>415</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8395,21 +8607,19 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>299</v>
+        <v>158</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8421,7 +8631,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8457,7 +8667,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8472,31 +8682,31 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>304</v>
+        <v>422</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>461</v>
+        <v>423</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8512,21 +8722,21 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>271</v>
+        <v>426</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8538,7 +8748,7 @@
         <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>81</v>
@@ -8550,13 +8760,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8574,7 +8784,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8589,31 +8799,31 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>277</v>
+        <v>431</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8629,21 +8839,19 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>467</v>
+        <v>158</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>469</v>
+        <v>436</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8691,7 +8899,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8700,37 +8908,37 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8746,16 +8954,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>475</v>
+        <v>442</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8770,7 +8978,7 @@
         <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>81</v>
@@ -8806,7 +9014,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8821,27 +9029,27 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>81</v>
+        <v>447</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8852,7 +9060,7 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8861,23 +9069,21 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>425</v>
+        <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8925,13 +9131,13 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
@@ -8940,27 +9146,27 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8980,19 +9186,21 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>190</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>191</v>
+        <v>457</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9004,7 +9212,7 @@
         <v>81</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>81</v>
@@ -9040,7 +9248,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>192</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9052,10 +9260,10 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>172</v>
+        <v>323</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9064,29 +9272,29 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9098,18 +9306,18 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9133,13 +9341,11 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9157,77 +9363,77 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>198</v>
+        <v>462</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>172</v>
+        <v>467</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>435</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>134</v>
+        <v>471</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>137</v>
+        <v>474</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>143</v>
+        <v>475</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9276,42 +9482,42 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>131</v>
+        <v>476</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>81</v>
+        <v>477</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9319,10 +9525,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9334,19 +9540,19 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>399</v>
+        <v>479</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9371,13 +9577,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9395,13 +9601,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9410,27 +9616,27 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>494</v>
+        <v>162</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9441,7 +9647,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9453,19 +9659,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>165</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9514,53 +9720,53 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>492</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>502</v>
+        <v>162</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9572,17 +9778,15 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>506</v>
+        <v>158</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>507</v>
+        <v>159</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9619,58 +9823,58 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>504</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>511</v>
+        <v>162</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>505</v>
+        <v>133</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9689,16 +9893,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>506</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>515</v>
+        <v>135</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>509</v>
+        <v>137</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9748,7 +9952,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>504</v>
+        <v>167</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9760,62 +9964,66 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>511</v>
+        <v>162</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>190</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -9863,22 +10071,22 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>192</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>172</v>
+        <v>131</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -9893,16 +10101,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9921,18 +10129,18 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>135</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9956,31 +10164,31 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>81</v>
+        <v>184</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>198</v>
+        <v>501</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9992,30 +10200,30 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>172</v>
+        <v>507</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10035,21 +10243,21 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10097,7 +10305,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10106,33 +10314,33 @@
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>131</v>
+        <v>255</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10143,7 +10351,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10152,21 +10360,23 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10190,13 +10400,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10214,13 +10424,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10229,27 +10439,27 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10272,18 +10482,18 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>537</v>
+        <v>363</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10331,7 +10541,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10340,33 +10550,33 @@
         <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>163</v>
+        <v>523</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10386,21 +10596,21 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>543</v>
+        <v>335</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10424,13 +10634,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10448,7 +10658,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10463,27 +10673,27 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>81</v>
+        <v>527</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10503,22 +10713,20 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>214</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>551</v>
+        <v>531</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10567,7 +10775,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10576,33 +10784,33 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>472</v>
+        <v>533</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>552</v>
+        <v>162</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>81</v>
+        <v>534</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10613,32 +10821,28 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>425</v>
+        <v>207</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10686,13 +10890,13 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
@@ -10701,10 +10905,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10716,12 +10920,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10732,7 +10936,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -10744,16 +10948,20 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>189</v>
+        <v>487</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>190</v>
+        <v>540</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10801,25 +11009,25 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>192</v>
+        <v>539</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>172</v>
+        <v>544</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>545</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10831,23 +11039,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>81</v>
@@ -10859,17 +11067,15 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10918,22 +11124,22 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>81</v>
@@ -10948,16 +11154,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>435</v>
+        <v>133</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10970,26 +11176,24 @@
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>436</v>
+        <v>135</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>437</v>
+        <v>164</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O76" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11037,7 +11241,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>438</v>
+        <v>167</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11052,7 +11256,7 @@
         <v>139</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
@@ -11067,46 +11271,48 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>563</v>
+        <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>564</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>565</v>
+        <v>499</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11154,42 +11360,42 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>562</v>
+        <v>500</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11209,19 +11415,23 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11245,13 +11455,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>570</v>
+        <v>113</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>571</v>
+        <v>114</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11269,7 +11479,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11284,22 +11494,1914 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AC80" s="2"/>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AL78" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AL80" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO94">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI93">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$94</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3530" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ipa/StructureDefinition/ipa-patient</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -491,10 +488,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pat-1:At least one of Patient.identifier.system or Patient.identifier.type or Patient.identifier.assigner SHALL be present {system.exists() or type.exists() or assigner.exists()}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -505,203 +498,6 @@
   </si>
   <si>
     <t>PID-3</t>
-  </si>
-  <si>
-    <t>Patient.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Patient.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Patient.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique within the system.</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Patient.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Patient.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>Patient.identifier:cpr</t>
@@ -728,30 +524,6 @@
   </si>
   <si>
     <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.use</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.type</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.system</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:cpr.assigner</t>
   </si>
   <si>
     <t>Patient.active</t>
@@ -779,11 +551,10 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pat-4:If Patient.link is present, then Patient.active SHALL be present {link.exists() implies active.exists()}</t>
-  </si>
-  <si>
     <t>statusCode</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
   <si>
     <t>FiveWs.status</t>
@@ -812,10 +583,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pat-2:Either Patient.name.given and/or Patient.name.family and/or Patient.name.text SHALL be present or a Data Absent Reason Extension SHALL be present. {(family.exists() or given.exists() or text.exists()) xor extension.where(url='http://hl7.org/fhir/StructureDefinition/data-absent-reason').exists()}ipa-pat-3:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -840,12 +607,38 @@
     <t>Patient.name.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>Patient.name:official.extension</t>
   </si>
   <si>
     <t>Patient.name.extension</t>
   </si>
   <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
     <t>Patient.name:official.use</t>
   </si>
   <si>
@@ -862,6 +655,9 @@
   </si>
   <si>
     <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>The use of a human name.</t>
@@ -1008,6 +804,10 @@
   </si>
   <si>
     <t>Patient.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
   </si>
   <si>
     <t>Time period when name was/is in use</t>
@@ -1455,6 +1255,10 @@
     <t>Patient.maritalStatus</t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
     <t>Marital (civil) status of a patient</t>
   </si>
   <si>
@@ -1462,6 +1266,9 @@
   </si>
   <si>
     <t>Most, if not all systems capture it.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>http://hl7.dk/fhir/core/ValueSet/dk-marital-status</t>
@@ -1662,6 +1469,10 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
     <t>Organization that is associated with the contact</t>
   </si>
   <si>
@@ -1944,10 +1755,6 @@
     <t>There are multiple use cases:   
 * Duplicate patient records due to the clerical errors associated with the difficulties of identifying humans consistently, and 
 * Distribution of patient information across multiple servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ipa-pat-4
-</t>
   </si>
   <si>
     <t>outboundLink</t>
@@ -2122,21 +1929,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2310,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO94"/>
+  <dimension ref="A1:AO78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.453125" customWidth="true" bestFit="true"/>
@@ -2337,7 +2129,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.2734375" customWidth="true" bestFit="true"/>
@@ -2480,7 +2272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2595,7 +2387,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -2712,7 +2504,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -2827,7 +2619,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2944,7 +2736,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -3061,7 +2853,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -3178,7 +2970,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3295,7 +3087,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -3412,7 +3204,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -3531,7 +3323,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -3550,7 +3342,7 @@
         <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>81</v>
@@ -3628,32 +3420,34 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AO11" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" hidden="true">
-      <c r="A12" t="s" s="2">
+      <c r="B12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3683,7 +3477,9 @@
         <v>160</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
       </c>
@@ -3731,19 +3527,19 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AG12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>162</v>
@@ -3755,121 +3551,125 @@
         <v>81</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3878,12 +3678,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3894,31 +3694,31 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3943,37 +3743,35 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AC14" s="2"/>
+      <c r="AD14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>81</v>
@@ -3982,29 +3780,31 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
@@ -4025,19 +3825,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -4062,13 +3862,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -4086,13 +3886,13 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -4101,27 +3901,27 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>81</v>
+        <v>182</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4141,10 +3941,10 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>190</v>
@@ -4152,12 +3952,8 @@
       <c r="M16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
-      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -4169,7 +3965,7 @@
         <v>81</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>81</v>
@@ -4205,7 +4001,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4217,10 +4013,10 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -4229,50 +4025,50 @@
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4286,7 +4082,7 @@
         <v>81</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>81</v>
@@ -4310,34 +4106,34 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
@@ -4346,18 +4142,18 @@
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>205</v>
+        <v>81</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4365,7 +4161,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
@@ -4374,28 +4170,32 @@
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>81</v>
@@ -4413,13 +4213,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4437,7 +4237,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4452,27 +4252,27 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="B19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" hidden="true">
-      <c r="A19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4495,18 +4295,20 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4554,7 +4356,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4569,63 +4371,61 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
+      <c r="B20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C20" t="s" s="2">
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
@@ -4673,19 +4473,19 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>227</v>
@@ -4703,23 +4503,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4728,18 +4528,20 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>159</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -4788,22 +4590,22 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4812,22 +4614,22 @@
         <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4843,20 +4645,18 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>135</v>
+        <v>240</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4893,19 +4693,19 @@
         <v>81</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>167</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4917,10 +4717,10 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
@@ -4929,18 +4729,18 @@
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4951,32 +4751,28 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>169</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
       </c>
@@ -5000,13 +4796,13 @@
         <v>81</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>81</v>
@@ -5024,13 +4820,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>176</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -5039,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -5048,18 +4844,18 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5082,19 +4878,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>179</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -5119,13 +4913,13 @@
         <v>81</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>81</v>
@@ -5143,7 +4937,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5158,7 +4952,7 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>177</v>
+        <v>259</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -5167,18 +4961,18 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>189</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5189,7 +4983,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5201,19 +4995,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5226,7 +5020,7 @@
         <v>81</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>81</v>
@@ -5262,13 +5056,13 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>81</v>
@@ -5277,27 +5071,27 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>198</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5305,13 +5099,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>
@@ -5320,18 +5114,20 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
       </c>
@@ -5343,7 +5139,7 @@
         <v>81</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>202</v>
+        <v>81</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>81</v>
@@ -5355,13 +5151,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5379,7 +5175,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5394,27 +5190,27 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>204</v>
+        <v>277</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5437,16 +5233,20 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
       </c>
@@ -5494,7 +5294,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5509,27 +5309,27 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5546,24 +5346,26 @@
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
@@ -5611,7 +5413,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>218</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5626,27 +5428,27 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>219</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5657,38 +5459,36 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>241</v>
+        <v>302</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q29" t="s" s="2">
-        <v>243</v>
-      </c>
+      <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
         <v>81</v>
       </c>
@@ -5732,42 +5532,42 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>162</v>
+        <v>305</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>246</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5778,32 +5578,28 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5839,90 +5635,88 @@
         <v>81</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AC30" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>254</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>255</v>
+        <v>172</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>248</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>135</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5958,19 +5752,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5982,32 +5776,34 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>255</v>
+        <v>172</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>256</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6028,13 +5824,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>158</v>
+        <v>311</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>160</v>
+        <v>313</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6085,22 +5881,22 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -6115,23 +5911,25 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -6143,17 +5941,15 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6190,19 +5986,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6217,7 +6013,7 @@
         <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6232,12 +6028,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6245,7 +6041,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
@@ -6263,29 +6059,29 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>269</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>81</v>
+        <v>324</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>81</v>
@@ -6297,13 +6093,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6321,7 +6117,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6336,7 +6132,7 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6345,18 +6141,18 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6379,20 +6175,18 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6404,7 +6198,7 @@
         <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>81</v>
+        <v>333</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>81</v>
@@ -6416,13 +6210,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6440,7 +6234,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6455,7 +6249,7 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>209</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6464,26 +6258,26 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>287</v>
+        <v>81</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -6498,18 +6292,20 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
       </c>
@@ -6521,7 +6317,7 @@
         <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>81</v>
+        <v>342</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>81</v>
@@ -6557,7 +6353,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>343</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6572,7 +6368,7 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -6581,22 +6377,22 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>296</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6615,17 +6411,15 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6638,7 +6432,7 @@
         <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>81</v>
@@ -6674,7 +6468,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6689,7 +6483,7 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>301</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6698,29 +6492,29 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
+        <v>352</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6732,13 +6526,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6753,7 +6547,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>81</v>
+        <v>356</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6789,13 +6583,13 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
@@ -6804,7 +6598,7 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6813,29 +6607,29 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6847,15 +6641,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6868,7 +6664,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -6904,13 +6700,13 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -6919,7 +6715,7 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6928,22 +6724,22 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6962,18 +6758,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -7021,7 +6815,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7036,7 +6830,7 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7045,29 +6839,29 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>377</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -7079,20 +6873,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>326</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7104,7 +6894,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -7140,13 +6930,13 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
@@ -7155,27 +6945,27 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7189,7 +6979,7 @@
         <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>81</v>
@@ -7198,20 +6988,18 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7235,13 +7023,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7259,7 +7047,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7274,27 +7062,27 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7308,7 +7096,7 @@
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>81</v>
@@ -7317,19 +7105,17 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>345</v>
+        <v>254</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7342,7 +7128,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>81</v>
+        <v>395</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7378,7 +7164,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7393,27 +7179,27 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>350</v>
+        <v>259</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>351</v>
+        <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7430,25 +7216,23 @@
         <v>81</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7473,13 +7257,11 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7497,7 +7279,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7512,27 +7294,27 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7543,7 +7325,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7552,22 +7334,22 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>410</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>366</v>
+        <v>412</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7616,13 +7398,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7631,27 +7413,27 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>368</v>
+        <v>414</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>172</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7662,7 +7444,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7674,16 +7456,20 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>158</v>
+        <v>417</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>159</v>
+        <v>418</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7731,46 +7517,46 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>161</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7789,18 +7575,20 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>425</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>135</v>
+        <v>426</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>164</v>
+        <v>427</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7836,19 +7624,19 @@
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>167</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7860,13 +7648,13 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>430</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7878,16 +7666,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7908,13 +7694,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>375</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>191</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7965,22 +7751,22 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
@@ -7995,25 +7781,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -8025,15 +7809,17 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>380</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>135</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8082,7 +7868,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8097,7 +7883,7 @@
         <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -8112,23 +7898,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -8140,19 +7926,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>436</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>437</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>386</v>
+        <v>137</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>387</v>
+        <v>143</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -8165,7 +7951,7 @@
         <v>81</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>81</v>
@@ -8177,13 +7963,13 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -8201,22 +7987,22 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>274</v>
+        <v>131</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8225,18 +8011,18 @@
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>392</v>
+        <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8247,7 +8033,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8256,21 +8042,21 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>440</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8282,7 +8068,7 @@
         <v>81</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>81</v>
@@ -8294,13 +8080,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8318,13 +8104,13 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
@@ -8333,27 +8119,27 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>274</v>
+        <v>445</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8373,22 +8159,20 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>281</v>
+        <v>450</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8401,7 +8185,7 @@
         <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>81</v>
@@ -8437,7 +8221,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8452,27 +8236,27 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>452</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8492,19 +8276,23 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8516,7 +8304,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8552,7 +8340,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8567,31 +8355,31 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>414</v>
+        <v>267</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8607,19 +8395,21 @@
         <v>81</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>158</v>
+        <v>299</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8631,7 +8421,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8667,7 +8457,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8682,31 +8472,31 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>422</v>
+        <v>304</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>425</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8722,21 +8512,21 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>426</v>
+        <v>271</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
       </c>
@@ -8748,7 +8538,7 @@
         <v>81</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>81</v>
@@ -8760,13 +8550,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8784,7 +8574,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8799,31 +8589,31 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>431</v>
+        <v>277</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8839,19 +8629,21 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>158</v>
+        <v>467</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8899,7 +8691,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8908,37 +8700,37 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>81</v>
+        <v>471</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8954,16 +8746,16 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8978,7 +8770,7 @@
         <v>81</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>81</v>
@@ -9014,7 +8806,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9029,27 +8821,27 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>446</v>
+        <v>477</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9060,7 +8852,7 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -9069,21 +8861,23 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>425</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -9131,13 +8925,13 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>81</v>
@@ -9146,27 +8940,27 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9186,21 +8980,19 @@
         <v>81</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>190</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>191</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>458</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9212,7 +9004,7 @@
         <v>81</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>81</v>
@@ -9248,7 +9040,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>192</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9260,10 +9052,10 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9272,29 +9064,29 @@
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9306,18 +9098,18 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>463</v>
+        <v>135</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9341,11 +9133,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9363,77 +9157,77 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>198</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>467</v>
+        <v>172</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>469</v>
+        <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>435</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>471</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>474</v>
+        <v>137</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>475</v>
+        <v>143</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9482,42 +9276,42 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>476</v>
+        <v>131</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>477</v>
+        <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9525,10 +9319,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9540,19 +9334,19 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>479</v>
+        <v>399</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9577,13 +9371,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9601,13 +9395,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9616,27 +9410,27 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>162</v>
+        <v>494</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9647,7 +9441,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9659,19 +9453,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>487</v>
+        <v>165</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9720,53 +9514,53 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>492</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>162</v>
+        <v>502</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>81</v>
+        <v>503</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9778,15 +9572,17 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>158</v>
+        <v>506</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>159</v>
+        <v>507</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9823,58 +9619,58 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>504</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>162</v>
+        <v>511</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="D65" t="s" s="2">
-        <v>133</v>
+        <v>505</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9893,16 +9689,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>134</v>
+        <v>506</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>135</v>
+        <v>515</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
+        <v>508</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>137</v>
+        <v>509</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9952,7 +9748,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>167</v>
+        <v>504</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9964,66 +9760,62 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>162</v>
+        <v>511</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>190</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10071,22 +9863,22 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>192</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -10101,16 +9893,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10129,18 +9921,18 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>502</v>
+        <v>135</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10164,31 +9956,31 @@
         <v>81</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>198</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10200,30 +9992,30 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>507</v>
+        <v>172</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10243,21 +10035,21 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10305,7 +10097,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10314,33 +10106,33 @@
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>255</v>
+        <v>131</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>513</v>
+        <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10351,7 +10143,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10360,23 +10152,21 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>326</v>
+        <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10400,13 +10190,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>533</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10424,13 +10214,13 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
@@ -10439,27 +10229,27 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>331</v>
+        <v>131</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10482,18 +10272,18 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>363</v>
+        <v>537</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10541,7 +10331,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10550,33 +10340,33 @@
         <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>368</v>
+        <v>162</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>523</v>
+        <v>163</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10596,21 +10386,21 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>335</v>
+        <v>543</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10634,13 +10424,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>340</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10658,7 +10448,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10673,27 +10463,27 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10713,20 +10503,22 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>214</v>
+        <v>467</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10775,7 +10567,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10784,33 +10576,33 @@
         <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>533</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>162</v>
+        <v>552</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10821,28 +10613,32 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>207</v>
+        <v>425</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10890,13 +10686,13 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
@@ -10905,10 +10701,10 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10920,12 +10716,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10936,7 +10732,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -10948,20 +10744,16 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>487</v>
+        <v>189</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>540</v>
+        <v>190</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11009,25 +10801,25 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>539</v>
+        <v>192</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>544</v>
+        <v>172</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>545</v>
+        <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -11039,23 +10831,23 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>81</v>
@@ -11067,15 +10859,17 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11124,22 +10918,22 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>81</v>
@@ -11154,16 +10948,16 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>133</v>
+        <v>435</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11176,24 +10970,26 @@
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>135</v>
+        <v>436</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11241,7 +11037,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>167</v>
+        <v>438</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11256,7 +11052,7 @@
         <v>139</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
@@ -11271,48 +11067,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>134</v>
+        <v>563</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>564</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>499</v>
+        <v>565</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11360,42 +11154,42 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>500</v>
+        <v>562</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>567</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11415,23 +11209,19 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11455,13 +11245,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>113</v>
+        <v>570</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>114</v>
+        <v>571</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11479,7 +11269,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>88</v>
@@ -11494,1914 +11284,22 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>555</v>
+        <v>172</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>556</v>
+        <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AC80" s="2"/>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="D81" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO94" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO94">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI93">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,6 +270,10 @@
   </si>
   <si>
     <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}marital-status-unknown-usage:Status in maritalStatus is unknown in a danish context. Consider mapping the value to UNK. See https://cpr.dk/borgere/hvad-staar-der-om-mig-i-cpr-registerindsigt/hvad-og-hvem-er-registreret-i-cpr-og-hvem-opdaterer-oplysninger-om-dig-i-cpr/ {maritalStatus.coding.where(code = 'P' and system = 'http://terminology.hl7.org/CodeSystem/v3-MaritalStatus').empty() or maritalStatus.coding.where(code = 'A' and system = 'http://terminology.hl7.org/CodeSystem/v3-MaritalStatus').empty()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -1047,7 +1051,7 @@
     <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
   </si>
   <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>both</t>
@@ -1922,10 +1926,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -2369,13 +2373,13 @@
         <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>81</v>
@@ -2389,10 +2393,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2403,7 +2407,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -2412,19 +2416,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2474,13 +2478,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2506,10 +2510,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2520,7 +2524,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -2529,16 +2533,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2589,19 +2593,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2621,10 +2625,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2635,28 +2639,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2706,19 +2710,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2738,10 +2742,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2752,7 +2756,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2764,16 +2768,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2799,13 +2803,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2823,19 +2827,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2855,21 +2859,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2881,16 +2885,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2940,22 +2944,22 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>81</v>
@@ -2972,14 +2976,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2998,16 +3002,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3057,7 +3061,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -3072,7 +3076,7 @@
         <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>81</v>
@@ -3089,14 +3093,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3115,16 +3119,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3174,7 +3178,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3186,10 +3190,10 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>81</v>
@@ -3206,14 +3210,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3226,25 +3230,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3293,7 +3297,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3305,10 +3309,10 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>81</v>
@@ -3325,10 +3329,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3336,7 +3340,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3348,20 +3352,20 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3398,17 +3402,17 @@
         <v>81</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3420,19 +3424,19 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>81</v>
@@ -3440,13 +3444,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>81</v>
@@ -3456,7 +3460,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>81</v>
@@ -3468,17 +3472,17 @@
         <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>81</v>
@@ -3527,7 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3536,13 +3540,13 @@
         <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>81</v>
@@ -3551,7 +3555,7 @@
         <v>81</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>81</v>
@@ -3559,10 +3563,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3573,103 +3577,103 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="P13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="R13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="P13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="R13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>81</v>
@@ -3680,10 +3684,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3703,22 +3707,22 @@
         <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3755,17 +3759,17 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3777,19 +3781,19 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
@@ -3797,13 +3801,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>81</v>
@@ -3813,7 +3817,7 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
@@ -3822,22 +3826,22 @@
         <v>81</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3886,7 +3890,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3898,19 +3902,19 @@
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -3918,10 +3922,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3932,7 +3936,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3944,13 +3948,13 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4001,13 +4005,13 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
@@ -4016,7 +4020,7 @@
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>81</v>
@@ -4033,14 +4037,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4059,16 +4063,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4106,19 +4110,19 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4130,10 +4134,10 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>81</v>
@@ -4150,10 +4154,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4161,41 +4165,41 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>81</v>
@@ -4213,13 +4217,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4237,22 +4241,22 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -4261,7 +4265,7 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4269,10 +4273,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4283,7 +4287,7 @@
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4292,22 +4296,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4356,22 +4360,22 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -4380,7 +4384,7 @@
         <v>81</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4388,21 +4392,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4411,19 +4415,19 @@
         <v>81</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4473,22 +4477,22 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4497,7 +4501,7 @@
         <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4505,14 +4509,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4528,19 +4532,19 @@
         <v>81</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4590,7 +4594,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4602,10 +4606,10 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4614,7 +4618,7 @@
         <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4622,10 +4626,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4645,16 +4649,16 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4705,7 +4709,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4717,10 +4721,10 @@
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
@@ -4729,7 +4733,7 @@
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4737,10 +4741,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4760,16 +4764,16 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4820,7 +4824,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4832,10 +4836,10 @@
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -4844,7 +4848,7 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4852,10 +4856,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4866,7 +4870,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4875,20 +4879,20 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4937,22 +4941,22 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4961,7 +4965,7 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -4969,10 +4973,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4992,22 +4996,22 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5056,7 +5060,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5068,19 +5072,19 @@
         <v>81</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5088,10 +5092,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5102,7 +5106,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5111,22 +5115,22 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5151,13 +5155,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5175,31 +5179,31 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5207,10 +5211,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5221,7 +5225,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5230,22 +5234,22 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5294,42 +5298,42 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5340,31 +5344,31 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5413,31 +5417,31 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5445,10 +5449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5468,22 +5472,22 @@
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5532,7 +5536,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5544,19 +5548,19 @@
         <v>81</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5564,10 +5568,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5578,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5590,13 +5594,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5647,13 +5651,13 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
@@ -5662,7 +5666,7 @@
         <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>81</v>
@@ -5679,14 +5683,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5705,16 +5709,16 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5752,19 +5756,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5776,10 +5780,10 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
@@ -5796,13 +5800,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="B32" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="C32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>81</v>
@@ -5812,7 +5816,7 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
@@ -5824,13 +5828,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5881,7 +5885,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5893,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>81</v>
@@ -5913,13 +5917,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>81</v>
@@ -5929,7 +5933,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5941,13 +5945,13 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5998,7 +6002,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6010,7 +6014,7 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>81</v>
@@ -6030,10 +6034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6044,31 +6048,31 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -6081,7 +6085,7 @@
         <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>81</v>
@@ -6093,13 +6097,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6117,22 +6121,22 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6141,7 +6145,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6149,10 +6153,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6163,7 +6167,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>81</v>
@@ -6172,19 +6176,19 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6198,7 +6202,7 @@
         <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>81</v>
@@ -6210,13 +6214,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6234,22 +6238,22 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6258,7 +6262,7 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6266,10 +6270,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6280,7 +6284,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6289,22 +6293,22 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6317,7 +6321,7 @@
         <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>81</v>
@@ -6353,22 +6357,22 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -6377,7 +6381,7 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6385,10 +6389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6408,16 +6412,16 @@
         <v>81</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6432,7 +6436,7 @@
         <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>81</v>
@@ -6468,7 +6472,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6480,10 +6484,10 @@
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6492,7 +6496,7 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6500,21 +6504,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6523,16 +6527,16 @@
         <v>81</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6547,7 +6551,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6583,22 +6587,22 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6607,7 +6611,7 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6615,21 +6619,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6638,19 +6642,19 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6664,7 +6668,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -6700,22 +6704,22 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6724,7 +6728,7 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6732,21 +6736,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6755,16 +6759,16 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6815,22 +6819,22 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -6839,7 +6843,7 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6847,21 +6851,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6870,16 +6874,16 @@
         <v>81</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6894,7 +6898,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -6930,22 +6934,22 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -6954,7 +6958,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6962,10 +6966,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6976,7 +6980,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -6985,19 +6989,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7047,22 +7051,22 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
@@ -7071,7 +7075,7 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7079,10 +7083,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7093,7 +7097,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7102,20 +7106,20 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -7128,7 +7132,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7164,22 +7168,22 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -7188,7 +7192,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7196,10 +7200,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7210,7 +7214,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7222,17 +7226,17 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -7257,11 +7261,11 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7279,31 +7283,31 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7311,10 +7315,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7325,7 +7329,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7337,19 +7341,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7398,31 +7402,31 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7430,10 +7434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7456,19 +7460,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7517,7 +7521,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7529,19 +7533,19 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7549,10 +7553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7575,19 +7579,19 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7636,7 +7640,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7648,13 +7652,13 @@
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7668,10 +7672,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7682,7 +7686,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7694,13 +7698,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7751,13 +7755,13 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
@@ -7766,7 +7770,7 @@
         <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>81</v>
@@ -7783,14 +7787,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7809,16 +7813,16 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7868,7 +7872,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7880,10 +7884,10 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -7900,14 +7904,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7920,25 +7924,25 @@
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -7987,7 +7991,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7999,10 +8003,10 @@
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8019,10 +8023,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8045,17 +8049,17 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8080,13 +8084,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8104,7 +8108,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8116,19 +8120,19 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8136,10 +8140,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8150,7 +8154,7 @@
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8162,17 +8166,17 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8221,31 +8225,31 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8253,10 +8257,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8279,19 +8283,19 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8340,7 +8344,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8352,19 +8356,19 @@
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8372,10 +8376,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8386,7 +8390,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8398,17 +8402,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8457,31 +8461,31 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8489,10 +8493,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8503,7 +8507,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8515,17 +8519,17 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8550,13 +8554,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8574,31 +8578,31 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8606,10 +8610,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8620,7 +8624,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8632,17 +8636,17 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8691,31 +8695,31 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8723,10 +8727,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8737,7 +8741,7 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8749,13 +8753,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8806,25 +8810,25 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
@@ -8838,10 +8842,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8864,19 +8868,19 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8925,7 +8929,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8937,13 +8941,13 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8957,10 +8961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8971,7 +8975,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8983,13 +8987,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9040,13 +9044,13 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
@@ -9055,7 +9059,7 @@
         <v>81</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>81</v>
@@ -9072,14 +9076,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9098,16 +9102,16 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9157,7 +9161,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9169,10 +9173,10 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
@@ -9189,14 +9193,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9209,25 +9213,25 @@
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9276,7 +9280,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9288,10 +9292,10 @@
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
@@ -9308,10 +9312,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9319,10 +9323,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9334,19 +9338,19 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9371,13 +9375,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9395,31 +9399,31 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9427,10 +9431,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9441,7 +9445,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9453,19 +9457,19 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9514,31 +9518,31 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -9546,14 +9550,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9572,16 +9576,16 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9619,17 +9623,17 @@
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9641,19 +9645,19 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9661,16 +9665,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9689,16 +9693,16 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9748,7 +9752,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9760,19 +9764,19 @@
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9780,10 +9784,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9794,7 +9798,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9806,13 +9810,13 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9863,13 +9867,13 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
@@ -9878,7 +9882,7 @@
         <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>81</v>
@@ -9895,14 +9899,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9921,16 +9925,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9968,19 +9972,19 @@
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9992,10 +9996,10 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>81</v>
@@ -10012,10 +10016,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10026,7 +10030,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10035,19 +10039,19 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10097,22 +10101,22 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
@@ -10129,10 +10133,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10143,7 +10147,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10152,19 +10156,19 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10190,13 +10194,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10214,22 +10218,22 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
@@ -10246,10 +10250,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10260,7 +10264,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10272,16 +10276,16 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10331,22 +10335,22 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
@@ -10355,7 +10359,7 @@
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
@@ -10363,10 +10367,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10377,7 +10381,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10386,19 +10390,19 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10448,22 +10452,22 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
@@ -10480,10 +10484,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10494,7 +10498,7 @@
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10503,22 +10507,22 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>81</v>
@@ -10567,25 +10571,25 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10599,10 +10603,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10619,25 +10623,25 @@
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
@@ -10686,7 +10690,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10698,13 +10702,13 @@
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10718,10 +10722,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10732,7 +10736,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
@@ -10744,13 +10748,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10801,13 +10805,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>81</v>
@@ -10816,7 +10820,7 @@
         <v>81</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>81</v>
@@ -10833,14 +10837,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10859,16 +10863,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10918,7 +10922,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10930,10 +10934,10 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>81</v>
@@ -10950,14 +10954,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10970,25 +10974,25 @@
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11037,7 +11041,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11049,10 +11053,10 @@
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
@@ -11069,10 +11073,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11080,10 +11084,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11092,19 +11096,19 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11154,31 +11158,31 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11186,10 +11190,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11197,10 +11201,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11209,16 +11213,16 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11245,13 +11249,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11269,25 +11273,25 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2936" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="582">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -528,6 +528,32 @@
   </si>
   <si>
     <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:x-ecpr</t>
+  </si>
+  <si>
+    <t>x-ecpr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-x-ecpr-identifier}
+</t>
+  </si>
+  <si>
+    <t>[DA] X-eCPR, tildelt fra den nationale eCPR service</t>
+  </si>
+  <si>
+    <t>Patient.identifier:d-ecpr</t>
+  </si>
+  <si>
+    <t>d-ecpr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-d-ecpr-identifier}
+</t>
+  </si>
+  <si>
+    <t>[DA] D-eCPR, decentral eCPR</t>
   </si>
   <si>
     <t>Patient.active</t>
@@ -2106,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.453125" customWidth="true" bestFit="true"/>
@@ -3566,9 +3592,11 @@
         <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3583,32 +3611,28 @@
         <v>81</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q13" t="s" s="2">
-        <v>171</v>
-      </c>
+      <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
         <v>81</v>
       </c>
@@ -3652,31 +3676,31 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
@@ -3684,12 +3708,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>81</v>
       </c>
@@ -3698,7 +3724,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>81</v>
@@ -3707,22 +3733,20 @@
         <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>81</v>
@@ -3759,17 +3783,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3778,22 +3804,22 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
@@ -3801,14 +3827,12 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3823,30 +3847,32 @@
         <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="P15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="P15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
         <v>81</v>
       </c>
@@ -3890,13 +3916,13 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -3905,16 +3931,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AN15" t="s" s="2">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -3922,10 +3948,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3936,7 +3962,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3945,19 +3971,23 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3993,43 +4023,41 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -4037,21 +4065,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4060,21 +4090,23 @@
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
       </c>
@@ -4110,19 +4142,19 @@
         <v>81</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4134,19 +4166,19 @@
         <v>81</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>81</v>
+        <v>192</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4154,10 +4186,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4165,7 +4197,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -4174,32 +4206,28 @@
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>81</v>
@@ -4217,13 +4245,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -4241,7 +4269,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4253,10 +4281,10 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -4265,7 +4293,7 @@
         <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4273,21 +4301,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>81</v>
@@ -4296,23 +4324,21 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
       </c>
@@ -4348,34 +4374,34 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>81</v>
@@ -4384,7 +4410,7 @@
         <v>81</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4392,14 +4418,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4412,30 +4438,32 @@
         <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>81</v>
@@ -4453,13 +4481,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4477,7 +4505,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4492,7 +4520,7 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>81</v>
@@ -4501,7 +4529,7 @@
         <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4509,21 +4537,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>81</v>
@@ -4535,18 +4563,20 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
       </c>
@@ -4594,13 +4624,13 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>81</v>
@@ -4609,7 +4639,7 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>81</v>
@@ -4618,7 +4648,7 @@
         <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4626,21 +4656,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4652,15 +4682,17 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4709,13 +4741,13 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
@@ -4724,7 +4756,7 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>81</v>
@@ -4733,7 +4765,7 @@
         <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4741,14 +4773,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4767,15 +4799,17 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4824,7 +4858,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4839,7 +4873,7 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>81</v>
@@ -4848,7 +4882,7 @@
         <v>81</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4856,10 +4890,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4870,7 +4904,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4882,18 +4916,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
       </c>
@@ -4941,13 +4973,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -4956,7 +4988,7 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>81</v>
@@ -4965,7 +4997,7 @@
         <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -4973,10 +5005,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4999,20 +5031,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>263</v>
+        <v>198</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>81</v>
       </c>
@@ -5060,7 +5088,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5075,16 +5103,16 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5092,10 +5120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5118,19 +5146,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>263</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5155,13 +5181,13 @@
         <v>81</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -5179,7 +5205,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5194,16 +5220,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>279</v>
+        <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5211,10 +5237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5225,7 +5251,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5237,19 +5263,19 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5298,13 +5324,13 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
@@ -5313,27 +5339,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>290</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5350,25 +5376,25 @@
         <v>81</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5393,13 +5419,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5417,7 +5443,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5432,16 +5458,16 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5449,10 +5475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5463,7 +5489,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5475,19 +5501,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5536,13 +5562,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5551,27 +5577,27 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>81</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5588,22 +5614,26 @@
         <v>81</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5651,7 +5681,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5663,19 +5693,19 @@
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5683,14 +5713,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5706,21 +5736,23 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>196</v>
+        <v>310</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
       </c>
@@ -5756,19 +5788,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>199</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5780,19 +5812,19 @@
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>173</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5800,14 +5832,12 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>81</v>
       </c>
@@ -5828,13 +5858,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>199</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>200</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5885,22 +5915,22 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
@@ -5917,23 +5947,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>81</v>
@@ -5945,15 +5973,17 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>317</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>136</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5990,19 +6020,19 @@
         <v>81</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6017,7 +6047,7 @@
         <v>140</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6034,12 +6064,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6054,13 +6086,13 @@
         <v>81</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>321</v>
@@ -6068,12 +6100,8 @@
       <c r="M34" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>324</v>
-      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6085,7 +6113,7 @@
         <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>81</v>
@@ -6097,13 +6125,13 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>326</v>
+        <v>81</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
@@ -6121,22 +6149,22 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>207</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6145,7 +6173,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>329</v>
+        <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6153,12 +6181,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6176,20 +6206,18 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>325</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -6202,7 +6230,7 @@
         <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>81</v>
@@ -6214,13 +6242,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -6238,22 +6266,22 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>207</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6262,7 +6290,7 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6270,10 +6298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6290,25 +6318,25 @@
         <v>81</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6321,7 +6349,7 @@
         <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>81</v>
@@ -6333,13 +6361,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6357,7 +6385,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6372,7 +6400,7 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -6381,7 +6409,7 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6389,10 +6417,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6403,7 +6431,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
@@ -6415,15 +6443,17 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -6436,7 +6466,7 @@
         <v>81</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>81</v>
@@ -6448,13 +6478,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6472,13 +6502,13 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
@@ -6487,7 +6517,7 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>218</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6496,7 +6526,7 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6504,14 +6534,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6530,16 +6560,20 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6551,7 +6585,7 @@
         <v>81</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>81</v>
@@ -6587,7 +6621,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6602,7 +6636,7 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>81</v>
@@ -6611,7 +6645,7 @@
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6619,21 +6653,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6645,17 +6679,15 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6668,7 +6700,7 @@
         <v>81</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>81</v>
@@ -6704,13 +6736,13 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -6719,7 +6751,7 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>81</v>
@@ -6728,7 +6760,7 @@
         <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6736,14 +6768,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6762,13 +6794,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6783,7 +6815,7 @@
         <v>81</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>81</v>
@@ -6819,7 +6851,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6834,7 +6866,7 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -6843,7 +6875,7 @@
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6851,14 +6883,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6877,15 +6909,17 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6898,7 +6932,7 @@
         <v>81</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>81</v>
@@ -6934,7 +6968,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6949,7 +6983,7 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
@@ -6958,7 +6992,7 @@
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -6966,14 +7000,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6992,17 +7026,15 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7051,7 +7083,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7066,7 +7098,7 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
@@ -7075,7 +7107,7 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7083,14 +7115,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7109,18 +7141,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>395</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7132,7 +7162,7 @@
         <v>81</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7168,7 +7198,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7183,7 +7213,7 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>260</v>
+        <v>391</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -7192,7 +7222,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7200,10 +7230,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7223,21 +7253,21 @@
         <v>81</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>400</v>
+        <v>198</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7261,11 +7291,13 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7283,7 +7315,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7298,16 +7330,16 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7315,10 +7347,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7338,22 +7370,20 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>410</v>
+        <v>263</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7366,7 +7396,7 @@
         <v>81</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>81</v>
@@ -7402,7 +7432,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7417,16 +7447,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>415</v>
+        <v>268</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7434,10 +7464,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7448,7 +7478,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7460,19 +7490,17 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7497,13 +7525,11 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7521,13 +7547,13 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>81</v>
@@ -7536,16 +7562,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>173</v>
+        <v>415</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7553,10 +7579,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7567,7 +7593,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7579,19 +7605,19 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -7640,31 +7666,31 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>431</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -7672,10 +7698,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7686,7 +7712,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7698,16 +7724,20 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>426</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>191</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7755,31 +7785,31 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>193</v>
+        <v>425</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>173</v>
+        <v>431</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7787,14 +7817,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7813,18 +7843,20 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>435</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>196</v>
+        <v>436</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7872,7 +7904,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>199</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7884,13 +7916,13 @@
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>439</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>173</v>
+        <v>440</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7904,46 +7936,42 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>199</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7991,22 +8019,22 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>439</v>
+        <v>201</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>81</v>
@@ -8023,14 +8051,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8049,18 +8077,18 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>441</v>
+        <v>136</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -8084,13 +8112,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8108,7 +8136,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>207</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8120,19 +8148,19 @@
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>446</v>
+        <v>181</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8140,43 +8168,45 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>451</v>
+        <v>144</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8225,31 +8255,31 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8257,10 +8287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8283,19 +8313,17 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>263</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8320,13 +8348,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>81</v>
+        <v>453</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8344,7 +8372,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8359,16 +8387,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>268</v>
+        <v>454</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8376,10 +8404,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8402,17 +8430,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8461,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8476,16 +8504,16 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>305</v>
+        <v>190</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8493,10 +8521,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8507,7 +8535,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8519,17 +8547,19 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>272</v>
+        <v>462</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>465</v>
+        <v>275</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8554,13 +8584,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>276</v>
+        <v>81</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -8578,13 +8608,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8593,16 +8623,16 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8610,10 +8640,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8636,17 +8666,17 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8695,7 +8725,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8704,22 +8734,22 @@
         <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>473</v>
+        <v>313</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8727,10 +8757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8753,16 +8783,18 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>255</v>
+        <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>280</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -8786,13 +8818,13 @@
         <v>81</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>81</v>
+        <v>285</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>81</v>
@@ -8810,7 +8842,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8825,16 +8857,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>478</v>
+        <v>286</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>81</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8842,10 +8874,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8856,7 +8888,7 @@
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -8868,19 +8900,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8929,31 +8959,31 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>81</v>
+        <v>480</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>485</v>
+        <v>181</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>482</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8961,10 +8991,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8987,13 +9017,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>191</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>192</v>
+        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9044,7 +9074,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>193</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9056,13 +9086,13 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>173</v>
+        <v>486</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
@@ -9083,7 +9113,7 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9102,18 +9132,20 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>136</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>196</v>
+        <v>489</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9161,7 +9193,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>199</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9173,13 +9205,13 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>173</v>
+        <v>492</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9193,46 +9225,42 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>437</v>
+        <v>199</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
       </c>
@@ -9280,22 +9308,22 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>439</v>
+        <v>201</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
@@ -9312,21 +9340,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9338,20 +9366,18 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>400</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>490</v>
+        <v>136</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>491</v>
+        <v>204</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9375,13 +9401,13 @@
         <v>81</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -9399,31 +9425,31 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>489</v>
+        <v>207</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>494</v>
+        <v>181</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9431,45 +9457,45 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>498</v>
+        <v>445</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>499</v>
+        <v>446</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>500</v>
+        <v>138</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>501</v>
+        <v>144</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9518,31 +9544,31 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>447</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>502</v>
+        <v>132</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -9550,21 +9576,21 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9576,18 +9602,20 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>507</v>
+        <v>408</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9611,35 +9639,37 @@
         <v>81</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
@@ -9648,16 +9678,16 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>173</v>
+        <v>503</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9665,23 +9695,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="C65" t="s" s="2">
-        <v>515</v>
-      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9693,18 +9721,20 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="O65" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N65" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9758,7 +9788,7 @@
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
@@ -9767,16 +9797,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9784,21 +9814,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9810,15 +9840,17 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>190</v>
+        <v>515</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>191</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -9855,43 +9887,41 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>193</v>
+        <v>513</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>173</v>
+        <v>520</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -9899,14 +9929,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="D67" t="s" s="2">
-        <v>134</v>
+        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9925,16 +9957,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>515</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>136</v>
+        <v>524</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>196</v>
+        <v>517</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>138</v>
+        <v>518</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9972,19 +10004,19 @@
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>199</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9996,19 +10028,19 @@
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>173</v>
+        <v>520</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10016,10 +10048,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10039,20 +10071,18 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>523</v>
+        <v>199</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10101,7 +10131,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>526</v>
+        <v>201</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10110,13 +10140,13 @@
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>527</v>
+        <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>81</v>
@@ -10133,21 +10163,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10156,19 +10186,19 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>530</v>
+        <v>136</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>531</v>
+        <v>204</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>532</v>
+        <v>138</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10194,46 +10224,46 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>404</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>533</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>534</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>81</v>
+        <v>205</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>81</v>
+        <v>206</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>535</v>
+        <v>207</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
@@ -10250,10 +10280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10273,19 +10303,19 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>538</v>
+        <v>198</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>161</v>
+        <v>532</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10335,7 +10365,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10344,13 +10374,13 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>162</v>
+        <v>535</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
@@ -10359,7 +10389,7 @@
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
@@ -10367,10 +10397,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10393,16 +10423,16 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10428,13 +10458,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10452,7 +10482,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10484,10 +10514,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10507,23 +10537,21 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>468</v>
+        <v>546</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>550</v>
+        <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10571,7 +10599,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10580,22 +10608,22 @@
         <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>473</v>
+        <v>163</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>553</v>
+        <v>81</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
@@ -10603,10 +10631,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10617,32 +10645,30 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10690,13 +10716,13 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
@@ -10705,10 +10731,10 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>559</v>
+        <v>132</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10722,10 +10748,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10745,19 +10771,23 @@
         <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>190</v>
+        <v>476</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>191</v>
+        <v>557</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
@@ -10805,7 +10835,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>193</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10817,13 +10847,13 @@
         <v>81</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>173</v>
+        <v>481</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10837,14 +10867,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10857,24 +10887,26 @@
         <v>81</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>136</v>
+        <v>563</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>196</v>
+        <v>564</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -10922,7 +10954,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>199</v>
+        <v>562</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10934,13 +10966,13 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>173</v>
+        <v>567</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10954,46 +10986,42 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>437</v>
+        <v>199</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11041,22 +11069,22 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>439</v>
+        <v>201</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>81</v>
@@ -11073,21 +11101,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>81</v>
@@ -11096,19 +11124,19 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>564</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>565</v>
+        <v>136</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>566</v>
+        <v>204</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>567</v>
+        <v>138</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11158,31 +11186,31 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>563</v>
+        <v>207</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11190,42 +11218,46 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>570</v>
+        <v>445</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11249,57 +11281,289 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="Z78" t="s" s="2">
+      <c r="B79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K79" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="AA78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AG78" t="s" s="2">
+      <c r="L79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG79" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AH78" t="s" s="2">
+      <c r="AH79" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AI78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AK79" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3011" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1427,10 +1427,7 @@
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
   </si>
   <si>
-    <t>The nature of the relationship between a patient and a contact person for that patient.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-RelatedPersonRelationshipTypes</t>
   </si>
   <si>
     <t>code</t>
@@ -2159,8 +2156,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.6640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.2734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8350,11 +8347,9 @@
       <c r="X53" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Y53" t="s" s="2">
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8387,7 +8382,7 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>181</v>
@@ -8396,7 +8391,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8404,10 +8399,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8433,14 +8428,14 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8489,7 +8484,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8513,7 +8508,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8521,10 +8516,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8550,13 +8545,13 @@
         <v>271</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>275</v>
@@ -8608,7 +8603,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8632,7 +8627,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8640,10 +8635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8669,14 +8664,14 @@
         <v>308</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8720,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8749,7 +8744,7 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8757,10 +8752,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8789,11 +8784,11 @@
         <v>280</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8842,7 +8837,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8866,7 +8861,7 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8874,10 +8869,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8900,17 +8895,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8959,7 +8954,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8968,13 +8963,13 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>181</v>
@@ -8983,7 +8978,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8991,10 +8986,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9020,10 +9015,10 @@
         <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9074,7 +9069,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9089,7 +9084,7 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>181</v>
@@ -9106,10 +9101,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9135,16 +9130,16 @@
         <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9193,7 +9188,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9208,10 +9203,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9225,10 +9220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9340,10 +9335,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9457,10 +9452,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9576,10 +9571,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9605,16 +9600,16 @@
         <v>408</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9658,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9678,16 +9673,16 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9695,10 +9690,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9724,16 +9719,16 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9782,7 +9777,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9797,16 +9792,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9814,14 +9809,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9840,16 +9835,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9887,7 +9882,7 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
@@ -9897,7 +9892,7 @@
         <v>152</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9912,7 +9907,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>181</v>
@@ -9921,7 +9916,7 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -9929,16 +9924,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="B67" t="s" s="2">
+      <c r="D67" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9957,16 +9952,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10016,7 +10011,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10031,7 +10026,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>181</v>
@@ -10040,7 +10035,7 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10048,10 +10043,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10163,10 +10158,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10280,10 +10275,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10309,13 +10304,13 @@
         <v>198</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10365,7 +10360,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10374,7 +10369,7 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
@@ -10397,10 +10392,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10426,13 +10421,13 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10461,28 +10456,28 @@
         <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10514,10 +10509,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10540,16 +10535,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10599,7 +10594,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10631,10 +10626,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10660,13 +10655,13 @@
         <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10716,7 +10711,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10748,10 +10743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10774,19 +10769,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10835,7 +10830,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10850,10 +10845,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10867,10 +10862,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10896,16 +10891,16 @@
         <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10954,7 +10949,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10969,7 +10964,7 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>181</v>
@@ -10986,10 +10981,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11101,10 +11096,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11218,10 +11213,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11337,10 +11332,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11363,16 +11358,16 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11422,7 +11417,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>89</v>
@@ -11446,7 +11441,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11454,10 +11449,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11483,10 +11478,10 @@
         <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11516,11 +11511,11 @@
         <v>214</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11537,7 +11532,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11552,7 +11547,7 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>181</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3011" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="582">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1427,7 +1427,10 @@
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
   </si>
   <si>
-    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-RelatedPersonRelationshipTypes</t>
+    <t>The nature of the relationship between a patient and a contact person for that patient.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
   </si>
   <si>
     <t>code</t>
@@ -2156,8 +2159,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="71.51171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.6640625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.2734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8347,9 +8350,11 @@
       <c r="X53" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Y53" s="2"/>
+      <c r="Y53" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8382,7 +8387,7 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>181</v>
@@ -8391,7 +8396,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8399,10 +8404,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8428,14 +8433,14 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8484,7 +8489,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8508,7 +8513,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8516,10 +8521,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8545,13 +8550,13 @@
         <v>271</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>275</v>
@@ -8603,7 +8608,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8627,7 +8632,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8635,10 +8640,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8664,14 +8669,14 @@
         <v>308</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8720,7 +8725,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8744,7 +8749,7 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8752,10 +8757,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8784,11 +8789,11 @@
         <v>280</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8837,7 +8842,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8861,7 +8866,7 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8869,10 +8874,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8895,17 +8900,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8954,7 +8959,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8963,13 +8968,13 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>181</v>
@@ -8978,7 +8983,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8986,10 +8991,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9015,10 +9020,10 @@
         <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9069,7 +9074,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9084,7 +9089,7 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>181</v>
@@ -9101,10 +9106,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9130,16 +9135,16 @@
         <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9188,7 +9193,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9203,10 +9208,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9220,10 +9225,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9335,10 +9340,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9452,10 +9457,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9571,10 +9576,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9600,16 +9605,16 @@
         <v>408</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9658,7 +9663,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9673,16 +9678,16 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9690,10 +9695,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9719,16 +9724,16 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9777,7 +9782,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9792,16 +9797,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9809,14 +9814,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9835,16 +9840,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9882,7 +9887,7 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
@@ -9892,7 +9897,7 @@
         <v>152</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9907,7 +9912,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>181</v>
@@ -9916,7 +9921,7 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -9924,16 +9929,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9952,16 +9957,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10011,7 +10016,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10026,7 +10031,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>181</v>
@@ -10035,7 +10040,7 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10043,10 +10048,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10158,10 +10163,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10275,10 +10280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10304,13 +10309,13 @@
         <v>198</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10360,7 +10365,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10369,7 +10374,7 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
@@ -10392,10 +10397,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10421,13 +10426,13 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10456,10 +10461,10 @@
         <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10477,7 +10482,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10509,10 +10514,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10535,16 +10540,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10594,7 +10599,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10626,10 +10631,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10655,13 +10660,13 @@
         <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10711,7 +10716,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10743,10 +10748,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10769,19 +10774,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10830,7 +10835,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10845,10 +10850,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10862,10 +10867,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10891,16 +10896,16 @@
         <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10949,7 +10954,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10964,7 +10969,7 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>181</v>
@@ -10981,10 +10986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11096,10 +11101,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11213,10 +11218,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11332,10 +11337,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11358,16 +11363,16 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11417,7 +11422,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>89</v>
@@ -11441,7 +11446,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11449,10 +11454,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11478,10 +11483,10 @@
         <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11511,10 +11516,10 @@
         <v>214</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
@@ -11532,7 +11537,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11547,7 +11552,7 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>181</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3012" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3011" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1427,10 +1427,7 @@
     <t>Used to determine which contact person is the most relevant to approach, depending on circumstances.</t>
   </si>
   <si>
-    <t>The nature of the relationship between a patient and a contact person for that patient.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.dk/fhir/core/ValueSet/dk-core-RelatedPersonRelationshipTypes</t>
   </si>
   <si>
     <t>code</t>
@@ -2159,8 +2156,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="71.51171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.6640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.2734375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8350,11 +8347,9 @@
       <c r="X53" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="Y53" t="s" s="2">
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8387,7 +8382,7 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>181</v>
@@ -8396,7 +8391,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8404,10 +8399,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8433,14 +8428,14 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8489,7 +8484,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8513,7 +8508,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8521,10 +8516,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8550,13 +8545,13 @@
         <v>271</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>275</v>
@@ -8608,7 +8603,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8632,7 +8627,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8640,10 +8635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8669,14 +8664,14 @@
         <v>308</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8720,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8749,7 +8744,7 @@
         <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8757,10 +8752,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8789,11 +8784,11 @@
         <v>280</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8842,7 +8837,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8866,7 +8861,7 @@
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8874,10 +8869,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8900,17 +8895,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8959,7 +8954,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8968,13 +8963,13 @@
         <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>181</v>
@@ -8983,7 +8978,7 @@
         <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8991,10 +8986,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9020,10 +9015,10 @@
         <v>263</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9074,7 +9069,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9089,7 +9084,7 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>181</v>
@@ -9106,10 +9101,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9135,16 +9130,16 @@
         <v>434</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9193,7 +9188,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9208,10 +9203,10 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
@@ -9225,10 +9220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9340,10 +9335,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9457,10 +9452,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9576,10 +9571,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9605,16 +9600,16 @@
         <v>408</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9658,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>89</v>
@@ -9678,16 +9673,16 @@
         <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9695,10 +9690,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9724,16 +9719,16 @@
         <v>174</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9782,7 +9777,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9797,16 +9792,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9814,14 +9809,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9840,16 +9835,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9887,7 +9882,7 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
@@ -9897,7 +9892,7 @@
         <v>152</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9912,7 +9907,7 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>181</v>
@@ -9921,7 +9916,7 @@
         <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>81</v>
@@ -9929,16 +9924,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="B67" t="s" s="2">
+      <c r="D67" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9957,16 +9952,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10016,7 +10011,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10031,7 +10026,7 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>181</v>
@@ -10040,7 +10035,7 @@
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10048,10 +10043,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10163,10 +10158,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10280,10 +10275,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10309,13 +10304,13 @@
         <v>198</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10365,7 +10360,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10374,7 +10369,7 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
@@ -10397,10 +10392,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10426,13 +10421,13 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10461,28 +10456,28 @@
         <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="Z71" t="s" s="2">
+      <c r="AA71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10514,10 +10509,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10540,16 +10535,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10599,7 +10594,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10631,10 +10626,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10660,13 +10655,13 @@
         <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10716,7 +10711,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10748,10 +10743,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10774,19 +10769,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10835,7 +10830,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10850,10 +10845,10 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10867,10 +10862,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10896,16 +10891,16 @@
         <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10954,7 +10949,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10969,7 +10964,7 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>181</v>
@@ -10986,10 +10981,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11101,10 +11096,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11218,10 +11213,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11337,10 +11332,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11363,16 +11358,16 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11422,7 +11417,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>89</v>
@@ -11446,7 +11441,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11454,10 +11449,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11483,10 +11478,10 @@
         <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11516,11 +11511,11 @@
         <v>214</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11537,7 +11532,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11552,7 +11547,7 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>181</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1799,7 +1799,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -2142,7 +2142,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="83.171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="124.08203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3011" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3011" uniqueCount="583">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1616,7 +1616,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
 </t>
   </si>
   <si>
@@ -1645,6 +1645,10 @@
   </si>
   <si>
     <t>referencedSORUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+</t>
   </si>
   <si>
     <t>[DA] Praktiserende læges SOR-id på sundhedsinstistutionsniveau</t>
@@ -1750,6 +1754,10 @@
   </si>
   <si>
     <t>Patient.managingOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization)
+</t>
   </si>
   <si>
     <t>Organization that is the custodian of the patient record</t>
@@ -2142,7 +2150,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="124.08203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="187.47265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -9952,10 +9960,10 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>516</v>
@@ -10043,10 +10051,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10158,10 +10166,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10275,10 +10283,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10304,13 +10312,13 @@
         <v>198</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10360,7 +10368,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10369,7 +10377,7 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
@@ -10392,10 +10400,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10421,13 +10429,13 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10456,10 +10464,10 @@
         <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10477,7 +10485,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10509,10 +10517,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10535,16 +10543,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
         <v>161</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10594,7 +10602,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10626,10 +10634,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10655,13 +10663,13 @@
         <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10711,7 +10719,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10743,10 +10751,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10769,19 +10777,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>475</v>
+        <v>557</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
@@ -10830,7 +10838,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10848,7 +10856,7 @@
         <v>480</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
@@ -10862,10 +10870,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10891,16 +10899,16 @@
         <v>434</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -10949,7 +10957,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10964,7 +10972,7 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>181</v>
@@ -10981,10 +10989,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11096,10 +11104,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11213,10 +11221,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11332,10 +11340,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11358,16 +11366,16 @@
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11417,7 +11425,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>89</v>
@@ -11441,7 +11449,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11449,10 +11457,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11478,10 +11486,10 @@
         <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11511,28 +11519,28 @@
         <v>214</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11547,7 +11555,7 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>181</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="661">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1853,7 +1853,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role)
 </t>
   </si>
   <si>
@@ -1882,6 +1882,10 @@
   </si>
   <si>
     <t>referencedSORUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+</t>
   </si>
   <si>
     <t>[DA] Praktiserende læges SOR-id på sundhedsinstistutionsniveau</t>
@@ -1987,6 +1991,10 @@
   </si>
   <si>
     <t>Patient.managingOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization)
+</t>
   </si>
   <si>
     <t>Organization that is the custodian of the patient record</t>
@@ -2398,7 +2406,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="124.08203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="187.47265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -13960,10 +13968,10 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>593</v>
@@ -14051,10 +14059,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14166,10 +14174,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14283,10 +14291,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14312,13 +14320,13 @@
         <v>159</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14368,7 +14376,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14377,7 +14385,7 @@
         <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>101</v>
@@ -14400,10 +14408,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14429,13 +14437,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14464,10 +14472,10 @@
         <v>185</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14485,7 +14493,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14517,10 +14525,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14543,16 +14551,16 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>226</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14602,7 +14610,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14634,10 +14642,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14663,13 +14671,13 @@
         <v>159</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14719,7 +14727,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14751,10 +14759,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14777,19 +14785,19 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>215</v>
+        <v>634</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14838,7 +14846,7 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14856,7 +14864,7 @@
         <v>557</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
@@ -14870,10 +14878,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14899,16 +14907,16 @@
         <v>512</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -14957,7 +14965,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14966,13 +14974,13 @@
         <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>163</v>
@@ -14989,10 +14997,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15104,10 +15112,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15221,10 +15229,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15340,10 +15348,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15366,16 +15374,16 @@
         <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15425,7 +15433,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>89</v>
@@ -15449,7 +15457,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15457,10 +15465,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15486,10 +15494,10 @@
         <v>109</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15519,28 +15527,28 @@
         <v>174</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>89</v>
@@ -15555,7 +15563,7 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>163</v>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5006" uniqueCount="717">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1325,7 +1325,7 @@
     <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
   </si>
   <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
   </si>
   <si>
     <t>both</t>
@@ -1528,6 +1528,182 @@
   </si>
   <si>
     <t>XAD.12 / XAD.13 + XAD.14</t>
+  </si>
+  <si>
+    <t>Patient.address:official</t>
+  </si>
+  <si>
+    <t>An official address</t>
+  </si>
+  <si>
+    <t>An address for the individual.</t>
+  </si>
+  <si>
+    <t>Patient.address:official.id</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:regionalSubDivisionCodes</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official</t>
+  </si>
+  <si>
+    <t>address-official</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {address-official}
+</t>
+  </si>
+  <si>
+    <t>Indicate that this address is meant to be the 'official' address for that person. In Denmark this is the [address registered in the CPR-register](https://www.retsinformation.dk/eli/lta/2023/1010).</t>
+  </si>
+  <si>
+    <t>This extension allows to specify if this address is or it is not the official address, or to indicate that this is the official address for that country (true assumed).  Note: It does not make sense to repeat this extension without the valueCodeableConcept to specify jurisdictions.</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.id</t>
+  </si>
+  <si>
+    <t>Patient.address.extension.id</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.extension</t>
+  </si>
+  <si>
+    <t>Patient.address.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.url</t>
+  </si>
+  <si>
+    <t>Patient.address.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/address-official</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A,AD/@use[.='OR']</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.value[x]</t>
+  </si>
+  <si>
+    <t>Patient.address.extension.value[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t>Official address true/false</t>
+  </si>
+  <si>
+    <t>It specifies if this address is or it is not the official address.</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Patient.address:official.extension:address-official.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Official address for country X</t>
+  </si>
+  <si>
+    <t>It specifies that this address is the official address for the indicated country.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="DK"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/jurisdiction</t>
+  </si>
+  <si>
+    <t>Patient.address:official.use</t>
+  </si>
+  <si>
+    <t>Patient.address:official.type</t>
+  </si>
+  <si>
+    <t>Patient.address:official.text</t>
+  </si>
+  <si>
+    <t>Patient.address:official.line</t>
+  </si>
+  <si>
+    <t>Patient.address:official.city</t>
+  </si>
+  <si>
+    <t>Patient.address:official.district</t>
+  </si>
+  <si>
+    <t>Patient.address:official.state</t>
+  </si>
+  <si>
+    <t>Patient.address:official.postalCode</t>
+  </si>
+  <si>
+    <t>Patient.address:official.country</t>
+  </si>
+  <si>
+    <t>Patient.address:official.period</t>
   </si>
   <si>
     <t>Patient.maritalStatus</t>
@@ -2393,10 +2569,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO112"/>
+  <dimension ref="A1:AO134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="76.10546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.47265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.91796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -9801,16 +9977,14 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>387</v>
@@ -11480,9 +11654,11 @@
         <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11500,10 +11676,10 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>488</v>
@@ -11511,9 +11687,11 @@
       <c r="M78" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N78" s="2"/>
+      <c r="N78" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>490</v>
+        <v>392</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11538,11 +11716,13 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11560,13 +11740,13 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>387</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>81</v>
@@ -11575,16 +11755,16 @@
         <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>492</v>
+        <v>393</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>493</v>
+        <v>394</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>494</v>
+        <v>395</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11592,10 +11772,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>495</v>
+        <v>396</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11618,20 +11798,16 @@
         <v>81</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>496</v>
+        <v>159</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>497</v>
+        <v>160</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -11679,7 +11855,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>495</v>
+        <v>162</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11691,19 +11867,19 @@
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>501</v>
+        <v>163</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11711,14 +11887,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>397</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11737,20 +11913,18 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>504</v>
+        <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>505</v>
+        <v>136</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>506</v>
+        <v>165</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11786,19 +11960,19 @@
         <v>81</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>168</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11810,19 +11984,19 @@
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>509</v>
+        <v>163</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11830,12 +12004,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11844,7 +12020,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -11856,20 +12032,16 @@
         <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>512</v>
+        <v>400</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>513</v>
+        <v>401</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11917,7 +12089,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>511</v>
+        <v>168</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11929,13 +12101,13 @@
         <v>81</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>517</v>
+        <v>140</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
@@ -11949,12 +12121,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>81</v>
       </c>
@@ -11975,13 +12149,13 @@
         <v>81</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>159</v>
+        <v>405</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>160</v>
+        <v>406</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>161</v>
+        <v>407</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12032,22 +12206,22 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -12064,21 +12238,23 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="D83" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -12090,17 +12266,15 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>496</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>136</v>
+        <v>497</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -12164,7 +12338,7 @@
         <v>140</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>81</v>
@@ -12181,46 +12355,42 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>523</v>
+        <v>160</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12268,22 +12438,22 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>525</v>
+        <v>162</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>81</v>
@@ -12300,10 +12470,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>526</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12314,7 +12484,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12326,18 +12496,16 @@
         <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>529</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -12361,29 +12529,31 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>81</v>
+        <v>167</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>526</v>
+        <v>168</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12395,19 +12565,19 @@
         <v>81</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>531</v>
+        <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12415,10 +12585,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12426,7 +12596,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>89</v>
@@ -12441,24 +12611,24 @@
         <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
@@ -12500,10 +12670,10 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>89</v>
@@ -12512,19 +12682,19 @@
         <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>280</v>
+        <v>512</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12532,10 +12702,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12546,7 +12716,7 @@
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12558,20 +12728,16 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>351</v>
+        <v>515</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12607,43 +12773,41 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>356</v>
+        <v>132</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>542</v>
+        <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>81</v>
@@ -12651,12 +12815,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12677,18 +12843,16 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>388</v>
+        <v>263</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>546</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12697,7 +12861,7 @@
         <v>81</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>81</v>
@@ -12736,7 +12900,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12745,22 +12909,22 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -12768,12 +12932,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12794,18 +12960,16 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>360</v>
+        <v>529</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>550</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12814,7 +12978,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>81</v>
+        <v>531</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12831,11 +12995,9 @@
       <c r="X89" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y89" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>365</v>
+        <v>532</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12853,7 +13015,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12862,22 +13024,22 @@
         <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>366</v>
+        <v>132</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>551</v>
+        <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -12885,10 +13047,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>552</v>
+        <v>408</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12905,23 +13067,25 @@
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>553</v>
+        <v>409</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>555</v>
+        <v>412</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -12934,7 +13098,7 @@
         <v>81</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>81</v>
@@ -12946,13 +13110,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>81</v>
+        <v>414</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12970,7 +13134,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>552</v>
+        <v>416</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12979,22 +13143,22 @@
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>556</v>
+        <v>81</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>557</v>
+        <v>299</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>558</v>
+        <v>417</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13002,10 +13166,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>559</v>
+        <v>418</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13025,18 +13189,20 @@
         <v>81</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>560</v>
+        <v>419</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13049,7 +13215,7 @@
         <v>81</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>81</v>
@@ -13061,13 +13227,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -13085,7 +13251,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>559</v>
+        <v>425</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13100,16 +13266,16 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>562</v>
+        <v>299</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>81</v>
+        <v>426</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13117,10 +13283,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>563</v>
+        <v>427</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13131,7 +13297,7 @@
         <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>81</v>
@@ -13140,22 +13306,22 @@
         <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>512</v>
+        <v>159</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>564</v>
+        <v>428</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>565</v>
+        <v>429</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>566</v>
+        <v>430</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>567</v>
+        <v>306</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -13168,7 +13334,7 @@
         <v>81</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>81</v>
@@ -13204,13 +13370,13 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>563</v>
+        <v>432</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>81</v>
@@ -13219,16 +13385,16 @@
         <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>568</v>
+        <v>308</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13236,10 +13402,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>570</v>
+        <v>536</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>570</v>
+        <v>434</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,7 +13416,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -13259,16 +13425,16 @@
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>159</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>160</v>
+        <v>435</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>161</v>
+        <v>436</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13283,7 +13449,7 @@
         <v>81</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>81</v>
+        <v>437</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>81</v>
@@ -13319,22 +13485,22 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>162</v>
+        <v>438</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>163</v>
+        <v>439</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
@@ -13343,7 +13509,7 @@
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>81</v>
+        <v>440</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13351,21 +13517,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>441</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13374,20 +13540,18 @@
         <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>136</v>
+        <v>443</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
@@ -13400,7 +13564,7 @@
         <v>81</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>81</v>
@@ -13436,22 +13600,22 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>168</v>
+        <v>446</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>163</v>
+        <v>447</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>81</v>
@@ -13460,7 +13624,7 @@
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>81</v>
+        <v>448</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13468,46 +13632,44 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>572</v>
+        <v>538</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>572</v>
+        <v>449</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>522</v>
+        <v>450</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>523</v>
+        <v>451</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>524</v>
+        <v>452</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13519,7 +13681,7 @@
         <v>81</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>81</v>
+        <v>454</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>81</v>
@@ -13555,22 +13717,22 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>525</v>
+        <v>455</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>132</v>
+        <v>456</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>81</v>
@@ -13579,7 +13741,7 @@
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13587,18 +13749,18 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>539</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>458</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>89</v>
@@ -13610,23 +13772,19 @@
         <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>574</v>
+        <v>460</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13650,13 +13808,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13674,10 +13832,10 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>573</v>
+        <v>462</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>89</v>
@@ -13689,16 +13847,16 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>578</v>
+        <v>463</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>579</v>
+        <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>580</v>
+        <v>464</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13706,14 +13864,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>581</v>
+        <v>540</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>581</v>
+        <v>465</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>81</v>
+        <v>466</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13729,23 +13887,19 @@
         <v>81</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>582</v>
+        <v>467</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13757,7 +13911,7 @@
         <v>81</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>81</v>
+        <v>469</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>81</v>
@@ -13793,7 +13947,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>581</v>
+        <v>470</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13808,16 +13962,16 @@
         <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>586</v>
+        <v>471</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>587</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>588</v>
+        <v>472</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13825,21 +13979,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>541</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>473</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>590</v>
+        <v>81</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
@@ -13848,19 +14002,19 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>591</v>
+        <v>159</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>592</v>
+        <v>474</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>593</v>
+        <v>475</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>594</v>
+        <v>476</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13898,23 +14052,25 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AC98" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>589</v>
+        <v>477</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
@@ -13923,16 +14079,16 @@
         <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>596</v>
+        <v>478</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>597</v>
+        <v>479</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -13940,23 +14096,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>542</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>590</v>
+        <v>81</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>
@@ -13965,21 +14119,21 @@
         <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>600</v>
+        <v>208</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>601</v>
+        <v>481</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -13991,7 +14145,7 @@
         <v>81</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>81</v>
+        <v>484</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>81</v>
@@ -14027,13 +14181,13 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>589</v>
+        <v>485</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>81</v>
@@ -14042,16 +14196,16 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>596</v>
+        <v>348</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>597</v>
+        <v>486</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>81</v>
@@ -14059,10 +14213,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>543</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>543</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14085,16 +14239,18 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>160</v>
+        <v>544</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>161</v>
+        <v>545</v>
       </c>
       <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14118,13 +14274,11 @@
         <v>81</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>81</v>
+        <v>547</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>81</v>
@@ -14142,7 +14296,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>162</v>
+        <v>543</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14154,19 +14308,19 @@
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>163</v>
+        <v>548</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>81</v>
+        <v>549</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>81</v>
+        <v>550</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14174,21 +14328,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>604</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>605</v>
+        <v>551</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14200,18 +14354,20 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>135</v>
+        <v>552</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>136</v>
+        <v>553</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>165</v>
+        <v>554</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -14247,43 +14403,43 @@
         <v>81</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>168</v>
+        <v>551</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL101" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>81</v>
+        <v>558</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14291,10 +14447,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>606</v>
+        <v>559</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>607</v>
+        <v>559</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14305,7 +14461,7 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
@@ -14314,21 +14470,23 @@
         <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>159</v>
+        <v>560</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>608</v>
+        <v>561</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>609</v>
+        <v>562</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
       </c>
@@ -14376,31 +14534,31 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>611</v>
+        <v>559</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>132</v>
+        <v>565</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14408,10 +14566,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>613</v>
+        <v>567</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>614</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14422,7 +14580,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14431,21 +14589,23 @@
         <v>81</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>568</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>615</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>616</v>
+        <v>570</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14469,13 +14629,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>618</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>619</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14493,25 +14653,25 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>620</v>
+        <v>567</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>573</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>132</v>
+        <v>574</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
@@ -14525,10 +14685,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>621</v>
+        <v>575</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>622</v>
+        <v>575</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14551,17 +14711,15 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>623</v>
+        <v>159</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>624</v>
+        <v>160</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14610,7 +14768,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>626</v>
+        <v>162</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14619,13 +14777,13 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>81</v>
@@ -14634,7 +14792,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14642,21 +14800,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>627</v>
+        <v>576</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>576</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14665,19 +14823,19 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>629</v>
+        <v>136</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>630</v>
+        <v>165</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>631</v>
+        <v>138</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14727,22 +14885,22 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>632</v>
+        <v>168</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>81</v>
@@ -14759,45 +14917,45 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>81</v>
+        <v>578</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>634</v>
+        <v>135</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>635</v>
+        <v>579</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>636</v>
+        <v>580</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>637</v>
+        <v>138</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>638</v>
+        <v>144</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14846,25 +15004,25 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>633</v>
+        <v>581</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>557</v>
+        <v>132</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>639</v>
+        <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>81</v>
@@ -14878,10 +15036,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14895,28 +15053,26 @@
         <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>512</v>
+        <v>180</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>641</v>
+        <v>583</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -14941,13 +15097,11 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
@@ -14965,7 +15119,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>640</v>
+        <v>582</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14974,13 +15128,13 @@
         <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>645</v>
+        <v>81</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>646</v>
+        <v>587</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>163</v>
@@ -14989,7 +15143,7 @@
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -14997,10 +15151,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15023,16 +15177,18 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>159</v>
+        <v>273</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>160</v>
+        <v>590</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>161</v>
+        <v>591</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15080,7 +15236,7 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>162</v>
+        <v>589</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15092,19 +15248,19 @@
         <v>81</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL108" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>81</v>
+        <v>593</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>81</v>
@@ -15112,14 +15268,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>648</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>648</v>
+        <v>594</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15138,18 +15294,20 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>135</v>
+        <v>351</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>136</v>
+        <v>595</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>165</v>
+        <v>596</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15197,7 +15355,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>168</v>
+        <v>594</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15209,19 +15367,19 @@
         <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL109" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>81</v>
+        <v>598</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15229,45 +15387,43 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>135</v>
+        <v>388</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>523</v>
+        <v>600</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>144</v>
+        <v>602</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15316,31 +15472,31 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>525</v>
+        <v>599</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>132</v>
+        <v>393</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>81</v>
+        <v>603</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15348,10 +15504,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>650</v>
+        <v>604</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>650</v>
+        <v>604</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15359,7 +15515,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>89</v>
@@ -15371,21 +15527,21 @@
         <v>81</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>651</v>
+        <v>109</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>652</v>
+        <v>360</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15409,13 +15565,13 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15433,10 +15589,10 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>650</v>
+        <v>604</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>89</v>
@@ -15448,7 +15604,7 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>154</v>
+        <v>366</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>163</v>
@@ -15457,7 +15613,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>655</v>
+        <v>607</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15465,10 +15621,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15476,7 +15632,7 @@
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>89</v>
@@ -15488,19 +15644,21 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>657</v>
+        <v>609</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15524,13 +15682,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>658</v>
+        <v>81</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>659</v>
+        <v>81</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15548,22 +15706,22 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>81</v>
+        <v>612</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>660</v>
+        <v>613</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>163</v>
@@ -15572,14 +15730,2592 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>81</v>
+        <v>614</v>
       </c>
       <c r="AO112" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AC120" s="2"/>
+      <c r="AD120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO112">
+  <autoFilter ref="A1:AO134">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15589,7 +18325,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI111">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-patient.xlsx
+++ b/StructureDefinition-dk-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
